--- a/models/DCF_SN.xlsx
+++ b/models/DCF_SN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb10f4a09bcef627/Documents/GitHub/XD_Grad_Portfolio/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4249" documentId="8_{4CAA811A-3924-48A6-9DA9-F0A76AB10370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0DE6722-2832-41B2-B048-4F5F0A877EAC}"/>
+  <xr:revisionPtr revIDLastSave="4269" documentId="8_{4CAA811A-3924-48A6-9DA9-F0A76AB10370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22069D15-3898-4772-842C-863352BEAA5A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{074DC5BB-03BC-4711-88CA-6F8F6CA366FE}"/>
   </bookViews>
@@ -891,7 +891,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1"/>
@@ -943,12 +943,6 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1696,18 +1690,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
       <c r="C1" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
       <c r="D1" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
       <c r="E1" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
       <c r="F1" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
     </row>
@@ -1715,30 +1714,30 @@
       <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="45">
+      <c r="B2" s="43">
         <f>'[1]Income Statement'!G8</f>
         <v>865.81174197145447</v>
       </c>
-      <c r="C2" s="45">
+      <c r="C2" s="43">
         <f>'[1]Income Statement'!H8</f>
         <v>920.46118290715049</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="43">
         <f>'[1]Income Statement'!I8</f>
         <v>978.74063885457053</v>
       </c>
-      <c r="E2" s="45">
+      <c r="E2" s="43">
         <f>'[1]Income Statement'!J8</f>
         <v>1040.9023874430359</v>
       </c>
-      <c r="F2" s="45">
+      <c r="F2" s="43">
         <f>'[1]Income Statement'!K8</f>
         <v>1107.2169098036211</v>
       </c>
       <c r="H2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="46">
+      <c r="I2" s="44">
         <f>'[1]Balance Sheet'!$N$7</f>
         <v>0.10567499999999999</v>
       </c>
@@ -1747,7 +1746,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="5">
@@ -1784,23 +1783,23 @@
       <c r="A4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="43">
         <f>'[1]Income Statement'!G39</f>
         <v>474.10524395977473</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="43">
         <f>'[1]Income Statement'!H39</f>
         <v>504.03044047892519</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="43">
         <f>'[1]Income Statement'!I39</f>
         <v>535.94337759950497</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="43">
         <f>'[1]Income Statement'!J39</f>
         <v>569.98219868593901</v>
       </c>
-      <c r="F4" s="45">
+      <c r="F4" s="43">
         <f>'[1]Income Statement'!K39</f>
         <v>606.29501506130021</v>
       </c>
@@ -1819,23 +1818,23 @@
       <c r="A5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="43">
         <f>'[1]Balance Sheet'!G53</f>
         <v>-477.50310262561572</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="43">
         <f>'[1]Balance Sheet'!H53</f>
         <v>-507.64276964391172</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="43">
         <f>'[1]Balance Sheet'!I53</f>
         <v>-539.78442317572933</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="43">
         <f>'[1]Balance Sheet'!J53</f>
         <v>-574.06719664336379</v>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="43">
         <f>'[1]Balance Sheet'!K53</f>
         <v>-610.64026286698993</v>
       </c>
@@ -1851,23 +1850,23 @@
       <c r="A6" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="43">
         <f>-'[1]Balance Sheet'!$G$52</f>
         <v>-149.35645811619816</v>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="43">
         <f>-'[1]Balance Sheet'!$G$52</f>
         <v>-149.35645811619816</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="43">
         <f>-'[1]Balance Sheet'!$G$52</f>
         <v>-149.35645811619816</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="43">
         <f>-'[1]Balance Sheet'!$G$52</f>
         <v>-149.35645811619816</v>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="43">
         <f>-'[1]Balance Sheet'!$G$52</f>
         <v>-149.35645811619816</v>
       </c>
@@ -1880,7 +1879,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="40" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="6">
@@ -1973,7 +1972,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="39" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="5">
@@ -1992,7 +1991,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="39" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="5">
@@ -2031,7 +2030,7 @@
       <c r="A15" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="45">
+      <c r="B15" s="43">
         <f>'[1]Balance Sheet'!$F$22</f>
         <v>2</v>
       </c>
@@ -2048,7 +2047,7 @@
       <c r="A16" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="45">
+      <c r="B16" s="43">
         <f>'[1]Balance Sheet'!$F$28</f>
         <v>3123</v>
       </c>
@@ -2080,7 +2079,7 @@
       <c r="A17" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="45">
+      <c r="B17" s="43">
         <f>'[1]Balance Sheet'!$F$23</f>
         <v>0</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>9.9999999999999985E-3</v>
       </c>
       <c r="H17" s="13">
-        <f t="dataTable" ref="H17:L21" dt2D="1" dtr="1" r1="I4" r2="I12"/>
+        <f t="dataTable" ref="H17:L21" dt2D="1" dtr="1" r1="I4" r2="I12" ca="1"/>
         <v>20738.04588044636</v>
       </c>
       <c r="I17" s="13">
@@ -2109,7 +2108,7 @@
       <c r="A18" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="45">
+      <c r="B18" s="43">
         <f>'[1]Balance Sheet'!$F$24</f>
         <v>61</v>
       </c>
@@ -2137,7 +2136,7 @@
       <c r="A19" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="45">
+      <c r="B19" s="43">
         <f>'[1]Balance Sheet'!$F$30</f>
         <v>79</v>
       </c>
@@ -2164,7 +2163,7 @@
       <c r="A20" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="45">
+      <c r="B20" s="43">
         <f>'[1]Balance Sheet'!$F$29</f>
         <v>135</v>
       </c>
@@ -2192,7 +2191,7 @@
       <c r="A21" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="45">
+      <c r="B21" s="43">
         <f>'[1]Balance Sheet'!$F$31</f>
         <v>31</v>
       </c>
@@ -2220,7 +2219,7 @@
       <c r="A22" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="45">
+      <c r="B22" s="43">
         <f>'[1]Balance Sheet'!$F$32</f>
         <v>190</v>
       </c>
@@ -2235,7 +2234,7 @@
       <c r="A23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="45">
+      <c r="B23" s="43">
         <f>'[1]Balance Sheet'!$F$3</f>
         <v>619</v>
       </c>
@@ -2258,20 +2257,20 @@
       <c r="A24" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="45">
+      <c r="B24" s="43">
         <f>'[1]Balance Sheet'!$F$12</f>
         <v>16</v>
       </c>
       <c r="I24" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="J24" s="83">
+      <c r="J24" s="81">
         <f>L23/B36*2</f>
         <v>29.815580370856146</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="39" t="s">
         <v>24</v>
       </c>
       <c r="B25">
@@ -2281,7 +2280,7 @@
       <c r="I25" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="J25" s="83">
+      <c r="J25" s="81">
         <f>J24-B29</f>
         <v>-7.0044196291438539</v>
       </c>
@@ -2291,7 +2290,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="39" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="5">
@@ -2304,7 +2303,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="39" t="s">
         <v>55</v>
       </c>
       <c r="B27" s="9">
@@ -2325,15 +2324,15 @@
       <c r="L27" s="30"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="83">
+      <c r="B28" s="81">
         <f>B27*2</f>
         <v>38.841458982173258</v>
       </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83">
+      <c r="C28" s="81"/>
+      <c r="D28" s="81">
         <f t="shared" ref="D28" si="1">D27*2</f>
         <v>35.795197659661483</v>
       </c>
@@ -2365,21 +2364,21 @@
       <c r="A29" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="86">
+      <c r="B29" s="84">
         <f>DCF!$I$9</f>
         <v>36.82</v>
       </c>
-      <c r="C29" s="83"/>
-      <c r="D29" s="86">
+      <c r="C29" s="81"/>
+      <c r="D29" s="84">
         <f>DCF!$I$9</f>
         <v>36.82</v>
       </c>
-      <c r="G29" s="50">
+      <c r="G29" s="48">
         <f>G30-1</f>
         <v>10.08</v>
       </c>
       <c r="H29" s="13">
-        <f t="dataTable" ref="H29:L33" dt2D="1" dtr="1" r1="I4" r2="I13" ca="1"/>
+        <f t="dataTable" ref="H29:L33" dt2D="1" dtr="1" r1="I4" r2="I13"/>
         <v>16801.597649603467</v>
       </c>
       <c r="I29" s="13">
@@ -2396,10 +2395,10 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="84">
+      <c r="B30" s="82">
         <f>B28-B29</f>
         <v>2.0214589821732574</v>
       </c>
@@ -2407,7 +2406,7 @@
         <f>B30/B29</f>
         <v>5.4901113041098785E-2</v>
       </c>
-      <c r="D30" s="84">
+      <c r="D30" s="82">
         <f>D28-D29</f>
         <v>-1.0248023403385176</v>
       </c>
@@ -2415,7 +2414,7 @@
         <f>D30/D29</f>
         <v>-2.7832763181382877E-2</v>
       </c>
-      <c r="G30" s="50">
+      <c r="G30" s="48">
         <f>G31-1</f>
         <v>11.08</v>
       </c>
@@ -2436,7 +2435,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G31" s="50">
+      <c r="G31" s="48">
         <v>12.08</v>
       </c>
       <c r="H31" s="13">
@@ -2456,7 +2455,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G32" s="50">
+      <c r="G32" s="48">
         <f>G31+1</f>
         <v>13.08</v>
       </c>
@@ -2477,7 +2476,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G33" s="50">
+      <c r="G33" s="48">
         <f>G32+1</f>
         <v>14.08</v>
       </c>
@@ -2501,7 +2500,7 @@
       <c r="A34" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="47">
+      <c r="B34" s="45">
         <f>'[1]Income Statement'!$F$24</f>
         <v>873</v>
       </c>
@@ -2516,7 +2515,7 @@
       <c r="A35" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="47">
+      <c r="B35" s="45">
         <v>3</v>
       </c>
       <c r="H35" s="28" t="s">
@@ -2535,7 +2534,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="39" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="3">
@@ -2545,7 +2544,7 @@
       <c r="I36" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="J36" s="83">
+      <c r="J36" s="81">
         <f>L35/B36*2</f>
         <v>38.799657619187641</v>
       </c>
@@ -2554,7 +2553,7 @@
       <c r="I37" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="J37" s="83">
+      <c r="J37" s="81">
         <f>J36-B29</f>
         <v>1.9796576191876412</v>
       </c>
@@ -2589,7 +2588,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="124"/>
+      <c r="A1" s="122"/>
       <c r="B1" s="34" t="s">
         <v>50</v>
       </c>
@@ -2614,188 +2613,206 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="34"/>
       <c r="S1" s="35"/>
-      <c r="T1" s="57" t="s">
+      <c r="T1" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="37">
+      <c r="A2" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2024"))</f>
         <v>2024</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="H2" s="37">
+      <c r="H2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2024"))</f>
         <v>2024</v>
       </c>
-      <c r="I2" s="37">
+      <c r="I2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="J2" s="37">
+      <c r="J2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="K2" s="37">
+      <c r="K2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="L2" s="37">
+      <c r="L2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="N2" s="37">
+      <c r="N2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2024"))</f>
         <v>2024</v>
       </c>
-      <c r="O2" s="37">
+      <c r="O2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="P2" s="37">
+      <c r="P2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="Q2" s="37">
+      <c r="Q2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="R2" s="37">
+      <c r="R2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="S2" s="38">
+      <c r="S2" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="T2" s="56">
+      <c r="T2" s="54">
         <v>2024</v>
       </c>
-      <c r="U2" s="51"/>
+      <c r="U2" s="49"/>
       <c r="V2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="W2" s="46">
+      <c r="W2" s="44">
         <f>'[1]Balance Sheet'!$N$7</f>
         <v>0.10567499999999999</v>
       </c>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
       <c r="AA2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="52">
+      <c r="B3" s="50">
         <f>'[1]Income Statement'!$F$43</f>
         <v>2305</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="43">
         <f>'[1]Income Statement'!G43</f>
         <v>2413.6991302341535</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="43">
         <f>'[1]Income Statement'!H43</f>
         <v>2527.5242912334529</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="43">
         <f>'[1]Income Statement'!I43</f>
         <v>2646.7172162238094</v>
       </c>
-      <c r="F3" s="45">
+      <c r="F3" s="43">
         <f>'[1]Income Statement'!J43</f>
         <v>2771.5310380803335</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="46">
         <f>'[1]Income Statement'!K43</f>
         <v>2902.230826911697</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="43">
         <f>'[1]Income Statement'!$F$44</f>
         <v>1824</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="43">
         <f>'[1]Income Statement'!G44</f>
         <v>1972.7566005307594</v>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="43">
         <f>'[1]Income Statement'!H44</f>
         <v>2133.6450684965343</v>
       </c>
-      <c r="K3" s="45">
+      <c r="K3" s="43">
         <f>'[1]Income Statement'!I44</f>
         <v>2307.6548202118656</v>
       </c>
-      <c r="L3" s="45">
+      <c r="L3" s="43">
         <f>'[1]Income Statement'!J44</f>
         <v>2495.8559639909986</v>
       </c>
-      <c r="M3" s="48">
+      <c r="M3" s="46">
         <f>'[1]Income Statement'!K44</f>
         <v>2699.405880996329</v>
       </c>
-      <c r="N3" s="45">
+      <c r="N3" s="43">
         <f>'[1]Income Statement'!$F$45</f>
         <v>1681</v>
       </c>
-      <c r="O3" s="45">
+      <c r="O3" s="43">
         <f>'[1]Income Statement'!G45</f>
         <v>1789.1296699937484</v>
       </c>
-      <c r="P3" s="45">
+      <c r="P3" s="43">
         <f>'[1]Income Statement'!H45</f>
         <v>1904.2147388768226</v>
       </c>
-      <c r="Q3" s="45">
+      <c r="Q3" s="43">
         <f>'[1]Income Statement'!I45</f>
         <v>2026.7026099725886</v>
       </c>
-      <c r="R3" s="45">
+      <c r="R3" s="43">
         <f>'[1]Income Statement'!J45</f>
         <v>2157.0694656488554</v>
       </c>
-      <c r="S3" s="49">
+      <c r="S3" s="47">
         <f>'[1]Income Statement'!K45</f>
         <v>2295.8221185186958</v>
       </c>
-      <c r="T3" s="58">
+      <c r="T3" s="56">
         <f>'[1]Income Statement'!F2</f>
         <v>5810</v>
       </c>
-      <c r="U3" s="51"/>
+      <c r="U3" s="49"/>
       <c r="V3" s="33" t="s">
         <v>15</v>
       </c>
       <c r="W3" s="8">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="51"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
       <c r="AA3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="53">
         <v>265</v>
       </c>
       <c r="C4" s="5">
@@ -2814,11 +2831,11 @@
         <f t="shared" si="0"/>
         <v>318.63588941053723</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="38">
         <f t="shared" si="0"/>
         <v>333.66211242151832</v>
       </c>
-      <c r="H4" s="55">
+      <c r="H4" s="53">
         <v>437</v>
       </c>
       <c r="I4" s="5">
@@ -2837,11 +2854,11 @@
         <f t="shared" si="1"/>
         <v>597.96549137284342</v>
       </c>
-      <c r="M4" s="40">
+      <c r="M4" s="38">
         <f t="shared" si="1"/>
         <v>646.73265898870386</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="53">
         <v>399</v>
       </c>
       <c r="O4" s="5">
@@ -2860,15 +2877,15 @@
         <f t="shared" si="2"/>
         <v>511.99923664122144</v>
       </c>
-      <c r="S4" s="40">
+      <c r="S4" s="38">
         <f t="shared" si="2"/>
         <v>544.93338803626386</v>
       </c>
-      <c r="T4" s="59">
+      <c r="T4" s="57">
         <f>'[1]Income Statement'!F8</f>
         <v>886</v>
       </c>
-      <c r="U4" s="51"/>
+      <c r="U4" s="49"/>
       <c r="V4" s="33" t="s">
         <v>2</v>
       </c>
@@ -2876,14 +2893,14 @@
         <f>(((W8/(W8+W6))*W7)+((W6/(W8+W6))*W5))*(1-W2)</f>
         <v>5.7975388146743925E-2</v>
       </c>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
       <c r="AA4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="41" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="10">
@@ -2894,7 +2911,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="40"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="10">
         <f>H4/H3</f>
         <v>0.23958333333333334</v>
@@ -2903,7 +2920,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="40"/>
+      <c r="M5" s="38"/>
       <c r="N5" s="10">
         <f>N4/N3</f>
         <v>0.23735871505056513</v>
@@ -2912,9 +2929,9 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
       <c r="V5" s="33" t="s">
         <v>8</v>
       </c>
@@ -2922,11 +2939,11 @@
         <f>0.056</f>
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="42" t="s">
         <v>54</v>
       </c>
       <c r="B6" s="5">
@@ -2949,7 +2966,7 @@
         <f t="shared" si="3"/>
         <v>284.96404179707872</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="38">
         <f t="shared" si="3"/>
         <v>298.40236869137436</v>
       </c>
@@ -2973,7 +2990,7 @@
         <f t="shared" si="3"/>
         <v>534.77548807201822</v>
       </c>
-      <c r="M6" s="40">
+      <c r="M6" s="38">
         <f t="shared" si="3"/>
         <v>578.38918525007261</v>
       </c>
@@ -2997,7 +3014,7 @@
         <f t="shared" si="3"/>
         <v>457.89371730916037</v>
       </c>
-      <c r="S6" s="40">
+      <c r="S6" s="38">
         <f t="shared" si="3"/>
         <v>487.3475522555317</v>
       </c>
@@ -3014,25 +3031,25 @@
       <c r="Y6" s="5"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="44"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="40"/>
+      <c r="G7" s="38"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="40"/>
+      <c r="M7" s="38"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-      <c r="S7" s="40"/>
+      <c r="S7" s="38"/>
       <c r="T7" s="5"/>
       <c r="V7" s="33" t="s">
         <v>10</v>
@@ -3043,29 +3060,29 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="41" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="28">
         <v>213</v>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="51">
         <f>$B$9*'[1]Income Statement'!G39</f>
         <v>224.90961461788868</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="51">
         <f>$B$9*'[1]Income Statement'!H39</f>
         <v>239.10575461472399</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="51">
         <f>$B$9*'[1]Income Statement'!I39</f>
         <v>254.24485396145781</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="51">
         <f>$B$9*'[1]Income Statement'!J39</f>
         <v>270.39244614722719</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="52">
         <f>$B$9*'[1]Income Statement'!K39</f>
         <v>287.61879333642975</v>
       </c>
@@ -3088,7 +3105,7 @@
         <f>$H$9*'[1]Income Statement'!J39</f>
         <v>124.40591418980407</v>
       </c>
-      <c r="M8" s="39">
+      <c r="M8" s="37">
         <f>$H$9*'[1]Income Statement'!K39</f>
         <v>132.33165139422587</v>
       </c>
@@ -3111,7 +3128,7 @@
         <f>$N$9*'[1]Income Statement'!J39</f>
         <v>78.705782446610726</v>
       </c>
-      <c r="S8" s="39">
+      <c r="S8" s="37">
         <f>$N$9*'[1]Income Statement'!K39</f>
         <v>83.720024351449027</v>
       </c>
@@ -3128,7 +3145,7 @@
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="41" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="10">
@@ -3139,7 +3156,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="39"/>
+      <c r="G9" s="37"/>
       <c r="H9" s="10">
         <f>H8/'[1]Income Statement'!F39</f>
         <v>0.21826280623608019</v>
@@ -3148,7 +3165,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="39"/>
+      <c r="M9" s="37"/>
       <c r="N9" s="10">
         <f>N8/'[1]Income Statement'!F39</f>
         <v>0.13808463251670378</v>
@@ -3157,7 +3174,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="39"/>
+      <c r="S9" s="37"/>
       <c r="T9" s="1"/>
       <c r="V9" s="33" t="s">
         <v>12</v>
@@ -3167,25 +3184,25 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="44"/>
-      <c r="B10" s="41"/>
+      <c r="A10" s="42"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="40"/>
+      <c r="G10" s="38"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="40"/>
+      <c r="M10" s="38"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="40"/>
+      <c r="S10" s="38"/>
       <c r="T10" s="5"/>
       <c r="V10" s="33" t="s">
         <v>13</v>
@@ -3195,7 +3212,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="41" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="1">
@@ -3218,7 +3235,7 @@
         <f>'[1]Balance Sheet'!J53*$B$13</f>
         <v>-248.69337038701681</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="37">
         <f>'[1]Balance Sheet'!K53*$B$13</f>
         <v>-264.53729799291983</v>
       </c>
@@ -3242,7 +3259,7 @@
         <f>'[1]Balance Sheet'!J53*$H$13</f>
         <v>-169.08711016019231</v>
       </c>
-      <c r="M11" s="39">
+      <c r="M11" s="37">
         <f>'[1]Balance Sheet'!K53*$H$13</f>
         <v>-179.85942760597047</v>
       </c>
@@ -3266,7 +3283,7 @@
         <f>'[1]Balance Sheet'!J53*$N$13</f>
         <v>-156.28671609615469</v>
       </c>
-      <c r="S11" s="39">
+      <c r="S11" s="37">
         <f>'[1]Balance Sheet'!K53*$N$13</f>
         <v>-166.24353726809963</v>
       </c>
@@ -3279,7 +3296,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="41" t="s">
         <v>106</v>
       </c>
       <c r="B12" s="1">
@@ -3302,7 +3319,7 @@
         <f>DCF!E6*$B$13</f>
         <v>-64.703158750699558</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="37">
         <f>DCF!F6*$B$13</f>
         <v>-64.703158750699558</v>
       </c>
@@ -3326,7 +3343,7 @@
         <f>DCF!E6*$H$13</f>
         <v>-43.991804503539356</v>
       </c>
-      <c r="M12" s="39">
+      <c r="M12" s="37">
         <f>DCF!F6*$H$13</f>
         <v>-43.991804503539356</v>
       </c>
@@ -3350,7 +3367,7 @@
         <f>DCF!E6*$N$13</f>
         <v>-40.661494861959234</v>
       </c>
-      <c r="S12" s="39">
+      <c r="S12" s="37">
         <f>DCF!F6*$N$13</f>
         <v>-40.661494861959234</v>
       </c>
@@ -3363,7 +3380,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="41" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="10">
@@ -3374,7 +3391,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="39"/>
+      <c r="G13" s="37"/>
       <c r="H13" s="10">
         <f>(H3-H4)/((B3-B4)+(H3-H4)+(N3-N4))</f>
         <v>0.29454236568273517</v>
@@ -3383,7 +3400,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="39"/>
+      <c r="M13" s="37"/>
       <c r="N13" s="10">
         <f>(N3-N4)/((B3-B4)+(H3-H4)+(N3-N4))</f>
         <v>0.27224463792737313</v>
@@ -3392,7 +3409,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="39"/>
+      <c r="S13" s="37"/>
       <c r="T13" s="1"/>
       <c r="V13" s="33" t="s">
         <v>48</v>
@@ -3403,29 +3420,29 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
+      <c r="A14" s="41"/>
       <c r="B14" s="10"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="39"/>
+      <c r="G14" s="37"/>
       <c r="H14" s="10"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="39"/>
+      <c r="M14" s="37"/>
       <c r="N14" s="10"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="39"/>
+      <c r="S14" s="37"/>
       <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="42" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="5"/>
@@ -3445,7 +3462,7 @@
         <f t="shared" si="4"/>
         <v>241.95995880658955</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="38">
         <f t="shared" si="4"/>
         <v>256.78070528418471</v>
       </c>
@@ -3466,7 +3483,7 @@
         <f t="shared" si="4"/>
         <v>446.10248759809065</v>
       </c>
-      <c r="M15" s="40">
+      <c r="M15" s="38">
         <f t="shared" si="4"/>
         <v>486.86960453478866</v>
       </c>
@@ -3487,7 +3504,7 @@
         <f t="shared" si="4"/>
         <v>339.65128879765717</v>
       </c>
-      <c r="S15" s="40">
+      <c r="S15" s="38">
         <f t="shared" si="4"/>
         <v>364.16254447692188</v>
       </c>
@@ -3497,98 +3514,98 @@
       <c r="AA15"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61">
+      <c r="B16" s="59"/>
+      <c r="C16" s="59">
         <f>C15/((1+$W$4)^(C2-2024))</f>
         <v>190.47540270667787</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="59">
         <f>D15/((1+$W$4)^(D2-2024))</f>
         <v>191.51126259893149</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="59">
         <f>E15/((1+$W$4)^(E2-2024))</f>
         <v>192.39157969931165</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="59">
         <f>F15/((1+$W$4)^(F2-2024))</f>
         <v>193.12622116425743</v>
       </c>
-      <c r="G16" s="62">
+      <c r="G16" s="60">
         <f>G15/((1+$W$4)^(G2-2024))</f>
         <v>193.72450666737925</v>
       </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61">
+      <c r="H16" s="59"/>
+      <c r="I16" s="59">
         <f>I15/((1+$W$4)^(I2-2024))</f>
         <v>322.82060537470289</v>
       </c>
-      <c r="J16" s="61">
+      <c r="J16" s="59">
         <f>J15/((1+$W$4)^(J2-2024))</f>
         <v>333.83297608552834</v>
       </c>
-      <c r="K16" s="61">
+      <c r="K16" s="59">
         <f>K15/((1+$W$4)^(K2-2024))</f>
         <v>344.91157021628231</v>
       </c>
-      <c r="L16" s="61">
+      <c r="L16" s="59">
         <f>L15/((1+$W$4)^(L2-2024))</f>
         <v>356.06754153343797</v>
       </c>
-      <c r="M16" s="62">
+      <c r="M16" s="60">
         <f>M15/((1+$W$4)^(M2-2024))</f>
         <v>367.3117645091736</v>
       </c>
-      <c r="N16" s="61"/>
-      <c r="O16" s="61">
+      <c r="N16" s="59"/>
+      <c r="O16" s="59">
         <f>O15/((1+$W$4)^(O2-2024))</f>
         <v>259.54902927784417</v>
       </c>
-      <c r="P16" s="61">
+      <c r="P16" s="59">
         <f>P15/((1+$W$4)^(P2-2024))</f>
         <v>263.51288241466108</v>
       </c>
-      <c r="Q16" s="61">
+      <c r="Q16" s="59">
         <f>Q15/((1+$W$4)^(Q2-2024))</f>
         <v>267.36144679934995</v>
       </c>
-      <c r="R16" s="61">
+      <c r="R16" s="59">
         <f>R15/((1+$W$4)^(R2-2024))</f>
         <v>271.10093026381759</v>
       </c>
-      <c r="S16" s="62">
+      <c r="S16" s="60">
         <f>S15/((1+$W$4)^(S2-2024))</f>
         <v>274.73718945297367</v>
       </c>
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
+      <c r="A17" s="41"/>
       <c r="B17" s="11"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="39"/>
+      <c r="G17" s="37"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="39"/>
+      <c r="M17" s="37"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="39"/>
+      <c r="S17" s="37"/>
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="41" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="1">
@@ -3599,7 +3616,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="39"/>
+      <c r="G18" s="37"/>
       <c r="H18" s="1">
         <f>((M16*(1+$W$12))/($W$4-$W$12))/((1+$W$4)^5)</f>
         <v>7443.119041826928</v>
@@ -3608,7 +3625,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="39"/>
+      <c r="M18" s="37"/>
       <c r="N18" s="1">
         <f>((S16*(1+$W$12))/($W$4-$W$12))/((1+$W$4)^5)</f>
         <v>5567.2096673733668</v>
@@ -3617,14 +3634,14 @@
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="39"/>
+      <c r="S18" s="37"/>
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="111">
+      <c r="B19" s="109">
         <f>B18+SUM(C16:G16)</f>
         <v>4886.8167262570896</v>
       </c>
@@ -3632,8 +3649,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="111">
+      <c r="G19" s="37"/>
+      <c r="H19" s="109">
         <f>H18+SUM(I16:M16)</f>
         <v>9168.0634995460532</v>
       </c>
@@ -3641,8 +3658,8 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="111">
+      <c r="M19" s="37"/>
+      <c r="N19" s="109">
         <f>N18+SUM(O16:S16)</f>
         <v>6903.4711455820134</v>
       </c>
@@ -3650,7 +3667,7 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="39"/>
+      <c r="S19" s="37"/>
       <c r="T19" s="1"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -3659,19 +3676,19 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="39"/>
+      <c r="G20" s="37"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-      <c r="M20" s="39"/>
+      <c r="M20" s="37"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="39"/>
+      <c r="S20" s="37"/>
       <c r="T20" s="1"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -3679,19 +3696,19 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="39"/>
+      <c r="G21" s="37"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
-      <c r="M21" s="39"/>
+      <c r="M21" s="37"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="39"/>
+      <c r="S21" s="37"/>
       <c r="T21" s="1"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -4070,7 +4087,7 @@
       <c r="A28" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="65" t="s">
+      <c r="B28" s="63" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="30"/>
@@ -4078,7 +4095,7 @@
       <c r="E28" s="30"/>
       <c r="F28" s="30"/>
       <c r="G28" s="30"/>
-      <c r="H28" s="65" t="s">
+      <c r="H28" s="63" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="30"/>
@@ -4086,7 +4103,7 @@
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
       <c r="M28" s="30"/>
-      <c r="N28" s="65" t="s">
+      <c r="N28" s="63" t="s">
         <v>22</v>
       </c>
       <c r="O28" s="30"/>
@@ -4100,7 +4117,7 @@
       <c r="A29" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="66">
+      <c r="B29" s="64">
         <f>IF(B28="Bull",D26,IF(B28="Bear",F24,IF(B28="Central",E25,"Error")))</f>
         <v>6589.7657382722937</v>
       </c>
@@ -4108,8 +4125,8 @@
       <c r="D29" s="30"/>
       <c r="E29" s="30"/>
       <c r="F29" s="30"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="66">
+      <c r="G29" s="65"/>
+      <c r="H29" s="64">
         <f>IF(H28="Bull",J26,IF(H28="Bear",L24,IF(H28="Central",K25,"Error")))</f>
         <v>12396.005007706268</v>
       </c>
@@ -4117,8 +4134,8 @@
       <c r="J29" s="30"/>
       <c r="K29" s="30"/>
       <c r="L29" s="30"/>
-      <c r="M29" s="67"/>
-      <c r="N29" s="66">
+      <c r="M29" s="65"/>
+      <c r="N29" s="64">
         <f>IF(N28="Bull",P26,IF(N28="Bear",R24,IF(N28="Central",Q25,"Error")))</f>
         <v>9318.3088380657282</v>
       </c>
@@ -4126,7 +4143,7 @@
       <c r="P29" s="30"/>
       <c r="Q29" s="30"/>
       <c r="R29" s="30"/>
-      <c r="S29" s="67"/>
+      <c r="S29" s="65"/>
       <c r="T29" s="1"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
@@ -4176,7 +4193,7 @@
       <c r="A32" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="63">
+      <c r="B32" s="61">
         <f>B29+H29+N29-B31</f>
         <v>25318.079584044288</v>
       </c>
@@ -4203,7 +4220,7 @@
       <c r="A33" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="64">
+      <c r="B33" s="62">
         <f>B32/DCF!B36</f>
         <v>28.901917333383889</v>
       </c>
@@ -4227,10 +4244,10 @@
       <c r="T33" s="1"/>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="84">
+      <c r="B34" s="82">
         <f>B33*2</f>
         <v>57.803834666767777</v>
       </c>
@@ -4257,7 +4274,7 @@
       <c r="A35" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="83">
+      <c r="B35" s="81">
         <f>DCF!I9</f>
         <v>36.82</v>
       </c>
@@ -4267,7 +4284,7 @@
       <c r="A36" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="85">
+      <c r="B36" s="83">
         <f>B34-B35</f>
         <v>20.983834666767777</v>
       </c>
@@ -4305,7 +4322,7 @@
   <dimension ref="A1:BL57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.77734375" style="115" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.77734375" style="113" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
@@ -4325,438 +4342,486 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="113" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70" t="s">
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="70"/>
-      <c r="V2" s="70"/>
-      <c r="W2" s="70"/>
-      <c r="X2" s="70"/>
-      <c r="Y2" s="70"/>
-      <c r="Z2" s="70" t="s">
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="AA2" s="70"/>
-      <c r="AB2" s="70"/>
-      <c r="AC2" s="70"/>
-      <c r="AD2" s="70"/>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70" t="s">
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="AI2" s="70"/>
-      <c r="AJ2" s="70"/>
-      <c r="AK2" s="70"/>
-      <c r="AL2" s="70"/>
-      <c r="AM2" s="70"/>
-      <c r="AN2" s="70"/>
-      <c r="AO2" s="70"/>
-      <c r="AP2" s="70" t="s">
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="AQ2" s="70"/>
-      <c r="AR2" s="70"/>
-      <c r="AS2" s="70"/>
-      <c r="AT2" s="70"/>
-      <c r="AU2" s="70"/>
-      <c r="AV2" s="70"/>
-      <c r="AW2" s="70"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="68"/>
     </row>
     <row r="3" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="70">
+      <c r="A3" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="C3" s="70">
+      <c r="C3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="D3" s="70">
+      <c r="D3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="E3" s="70">
+      <c r="E3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="F3" s="70">
+      <c r="F3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="G3" s="70">
+      <c r="G3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2030"))</f>
         <v>2030</v>
       </c>
-      <c r="H3" s="70">
+      <c r="H3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2031"))</f>
         <v>2031</v>
       </c>
-      <c r="I3" s="70">
+      <c r="I3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2032"))</f>
         <v>2032</v>
       </c>
-      <c r="J3" s="70">
+      <c r="J3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="K3" s="70">
+      <c r="K3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="L3" s="70">
+      <c r="L3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="N3" s="70">
+      <c r="N3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="O3" s="70">
+      <c r="O3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2030"))</f>
         <v>2030</v>
       </c>
-      <c r="P3" s="70">
+      <c r="P3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2031"))</f>
         <v>2031</v>
       </c>
-      <c r="Q3" s="70">
+      <c r="Q3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2032"))</f>
         <v>2032</v>
       </c>
-      <c r="R3" s="70">
+      <c r="R3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="S3" s="70">
+      <c r="S3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="T3" s="70">
+      <c r="T3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="U3" s="70">
+      <c r="U3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="V3" s="70">
+      <c r="V3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="W3" s="70">
+      <c r="W3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2030"))</f>
         <v>2030</v>
       </c>
-      <c r="X3" s="70">
+      <c r="X3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2031"))</f>
         <v>2031</v>
       </c>
-      <c r="Y3" s="70">
+      <c r="Y3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2032"))</f>
         <v>2032</v>
       </c>
-      <c r="Z3" s="70">
+      <c r="Z3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="AA3" s="70">
+      <c r="AA3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="AB3" s="70">
+      <c r="AB3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="AC3" s="70">
+      <c r="AC3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="AD3" s="70">
+      <c r="AD3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="AE3" s="70">
+      <c r="AE3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2030"))</f>
         <v>2030</v>
       </c>
-      <c r="AF3" s="70">
+      <c r="AF3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2031"))</f>
         <v>2031</v>
       </c>
-      <c r="AG3" s="70">
+      <c r="AG3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2032"))</f>
         <v>2032</v>
       </c>
-      <c r="AH3" s="70">
+      <c r="AH3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="AI3" s="70">
+      <c r="AI3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="AJ3" s="70">
+      <c r="AJ3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="AK3" s="70">
+      <c r="AK3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="AL3" s="70">
+      <c r="AL3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="AM3" s="70">
+      <c r="AM3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2030"))</f>
         <v>2030</v>
       </c>
-      <c r="AN3" s="70">
+      <c r="AN3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2031"))</f>
         <v>2031</v>
       </c>
-      <c r="AO3" s="70">
+      <c r="AO3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2032"))</f>
         <v>2032</v>
       </c>
-      <c r="AP3" s="70">
+      <c r="AP3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
-      <c r="AQ3" s="70">
+      <c r="AQ3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
-      <c r="AR3" s="70">
+      <c r="AR3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
-      <c r="AS3" s="70">
+      <c r="AS3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
-      <c r="AT3" s="70">
+      <c r="AT3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
-      <c r="AU3" s="70">
+      <c r="AU3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2030"))</f>
         <v>2030</v>
       </c>
-      <c r="AV3" s="70">
+      <c r="AV3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2031"))</f>
         <v>2031</v>
       </c>
-      <c r="AW3" s="70">
+      <c r="AW3" s="4">
+        <f>YEAR(DATEVALUE("JAN-2032"))</f>
         <v>2032</v>
       </c>
-      <c r="BF3" s="110" t="s">
+      <c r="BF3" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="BG3" s="107" t="s">
+      <c r="BG3" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="BH3" s="107" t="s">
+      <c r="BH3" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="BI3" s="107" t="s">
+      <c r="BI3" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="BJ3" s="107" t="s">
+      <c r="BJ3" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="BK3" s="107" t="s">
+      <c r="BK3" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="BL3" s="108" t="s">
+      <c r="BL3" s="106" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="113" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="71">
+      <c r="B4" s="69">
         <f>BG17*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>291.363</v>
       </c>
-      <c r="C4" s="71">
+      <c r="C4" s="69">
         <f>B4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>292.73240609999999</v>
       </c>
-      <c r="D4" s="71">
+      <c r="D4" s="69">
         <f>C4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>294.10824840867002</v>
       </c>
-      <c r="E4" s="71">
+      <c r="E4" s="69">
         <f>D4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>295.4905571761908</v>
       </c>
-      <c r="F4" s="71">
+      <c r="F4" s="69">
         <f>E4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>296.8793627949189</v>
       </c>
-      <c r="G4" s="71">
+      <c r="G4" s="69">
         <f>F4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>298.27469580005504</v>
       </c>
-      <c r="H4" s="71">
+      <c r="H4" s="69">
         <f>G4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>299.6765868703153</v>
       </c>
-      <c r="I4" s="71">
+      <c r="I4" s="69">
         <f>H4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>301.08506682860582</v>
       </c>
-      <c r="J4" s="71">
+      <c r="J4" s="69">
         <f>BH17*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>218.52224999999999</v>
       </c>
-      <c r="K4" s="71">
+      <c r="K4" s="69">
         <f>J4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>219.54930457499998</v>
       </c>
-      <c r="L4" s="71">
+      <c r="L4" s="69">
         <f>K4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>220.58118630650247</v>
       </c>
-      <c r="M4" s="71">
+      <c r="M4" s="69">
         <f>L4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>221.61791788214302</v>
       </c>
-      <c r="N4" s="71">
+      <c r="N4" s="69">
         <f>M4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>222.65952209618911</v>
       </c>
-      <c r="O4" s="71">
+      <c r="O4" s="69">
         <f>N4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>223.7060218500412</v>
       </c>
-      <c r="P4" s="71">
+      <c r="P4" s="69">
         <f>O4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>224.75744015273639</v>
       </c>
-      <c r="Q4" s="71">
+      <c r="Q4" s="69">
         <f>P4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>225.81380012145425</v>
       </c>
-      <c r="R4" s="71">
+      <c r="R4" s="69">
         <f>BI17*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>337.57920000000001</v>
       </c>
-      <c r="S4" s="71">
+      <c r="S4" s="69">
         <f>R4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>339.16582224000001</v>
       </c>
-      <c r="T4" s="71">
+      <c r="T4" s="69">
         <f>S4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>340.75990160452801</v>
       </c>
-      <c r="U4" s="71">
+      <c r="U4" s="69">
         <f>T4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>342.36147314206931</v>
       </c>
-      <c r="V4" s="71">
+      <c r="V4" s="69">
         <f>U4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>343.97057206583702</v>
       </c>
-      <c r="W4" s="71">
+      <c r="W4" s="69">
         <f>V4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>345.58723375454645</v>
       </c>
-      <c r="X4" s="71">
+      <c r="X4" s="69">
         <f>W4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>347.21149375319277</v>
       </c>
-      <c r="Y4" s="71">
+      <c r="Y4" s="69">
         <f>X4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>348.84338777383277</v>
       </c>
-      <c r="Z4" s="71">
+      <c r="Z4" s="69">
         <f>BJ17*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>421.97400000000005</v>
       </c>
-      <c r="AA4" s="71">
+      <c r="AA4" s="69">
         <f>Z4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>423.95727780000004</v>
       </c>
-      <c r="AB4" s="71">
+      <c r="AB4" s="69">
         <f>AA4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>425.94987700566003</v>
       </c>
-      <c r="AC4" s="71">
+      <c r="AC4" s="69">
         <f>AB4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>427.95184142758666</v>
       </c>
-      <c r="AD4" s="71">
+      <c r="AD4" s="69">
         <f>AC4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>429.96321508229636</v>
       </c>
-      <c r="AE4" s="71">
+      <c r="AE4" s="69">
         <f>AD4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>431.98404219318314</v>
       </c>
-      <c r="AF4" s="71">
+      <c r="AF4" s="69">
         <f>AE4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>434.01436719149115</v>
       </c>
-      <c r="AG4" s="71">
+      <c r="AG4" s="69">
         <f>AF4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>436.05423471729114</v>
       </c>
-      <c r="AH4" s="71">
+      <c r="AH4" s="69">
         <f>BK17*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>182.95586999999998</v>
       </c>
-      <c r="AI4" s="71">
+      <c r="AI4" s="69">
         <f>AH4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>183.81576258899997</v>
       </c>
-      <c r="AJ4" s="71">
+      <c r="AJ4" s="69">
         <f>AI4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>184.67969667316828</v>
       </c>
-      <c r="AK4" s="71">
+      <c r="AK4" s="69">
         <f>AJ4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>185.54769124753219</v>
       </c>
-      <c r="AL4" s="71">
+      <c r="AL4" s="69">
         <f>AK4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>186.4197653963956</v>
       </c>
-      <c r="AM4" s="71">
+      <c r="AM4" s="69">
         <f>AL4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>187.29593829375867</v>
       </c>
-      <c r="AN4" s="71">
+      <c r="AN4" s="69">
         <f>AM4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>188.17622920373935</v>
       </c>
-      <c r="AO4" s="71">
+      <c r="AO4" s="69">
         <f>AN4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>189.06065748099692</v>
       </c>
-      <c r="AP4" s="71">
+      <c r="AP4" s="69">
         <f>BL17*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>365.91173999999995</v>
       </c>
-      <c r="AQ4" s="71">
+      <c r="AQ4" s="69">
         <f>AP4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>367.63152517799995</v>
       </c>
-      <c r="AR4" s="71">
+      <c r="AR4" s="69">
         <f>AQ4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>369.35939334633656</v>
       </c>
-      <c r="AS4" s="71">
+      <c r="AS4" s="69">
         <f>AR4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>371.09538249506437</v>
       </c>
-      <c r="AT4" s="71">
+      <c r="AT4" s="69">
         <f>AS4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>372.83953079279121</v>
       </c>
-      <c r="AU4" s="71">
+      <c r="AU4" s="69">
         <f>AT4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>374.59187658751733</v>
       </c>
-      <c r="AV4" s="71">
+      <c r="AV4" s="69">
         <f>AU4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>376.35245840747871</v>
       </c>
-      <c r="AW4" s="71">
+      <c r="AW4" s="69">
         <f>AV4*(1+$AZ$11)*(1-_xlfn.XLOOKUP(Scenario,AY7:AY9,BC7:BC9,,0))</f>
         <v>378.12131496199385</v>
       </c>
@@ -4764,1043 +4829,1043 @@
       <c r="BF4" t="s">
         <v>76</v>
       </c>
-      <c r="BG4" s="87">
+      <c r="BG4" s="85">
         <v>2027</v>
       </c>
-      <c r="BH4" s="87">
+      <c r="BH4" s="85">
         <v>2028</v>
       </c>
-      <c r="BI4" s="87">
+      <c r="BI4" s="85">
         <v>2027</v>
       </c>
-      <c r="BJ4" s="87">
+      <c r="BJ4" s="85">
         <v>2027</v>
       </c>
-      <c r="BK4" s="87">
+      <c r="BK4" s="85">
         <v>2027</v>
       </c>
-      <c r="BL4" s="109">
+      <c r="BL4" s="107">
         <v>2028</v>
       </c>
     </row>
     <row r="5" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A5" s="126" t="s">
+      <c r="A5" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="71"/>
-      <c r="V5" s="71"/>
-      <c r="W5" s="71"/>
-      <c r="X5" s="71"/>
-      <c r="Y5" s="71"/>
-      <c r="Z5" s="71"/>
-      <c r="AA5" s="71"/>
-      <c r="AB5" s="71"/>
-      <c r="AC5" s="71"/>
-      <c r="AD5" s="71"/>
-      <c r="AE5" s="71"/>
-      <c r="AF5" s="71"/>
-      <c r="AG5" s="71"/>
-      <c r="AH5" s="71"/>
-      <c r="AI5" s="71"/>
-      <c r="AJ5" s="71"/>
-      <c r="AK5" s="71"/>
-      <c r="AL5" s="71"/>
-      <c r="AM5" s="71"/>
-      <c r="AN5" s="71"/>
-      <c r="AO5" s="71"/>
-      <c r="AP5" s="71"/>
-      <c r="AQ5" s="71"/>
-      <c r="AR5" s="71"/>
-      <c r="AS5" s="71"/>
-      <c r="AT5" s="71"/>
-      <c r="AU5" s="71"/>
-      <c r="AV5" s="71"/>
-      <c r="AW5" s="71"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="69"/>
+      <c r="Y5" s="69"/>
+      <c r="Z5" s="69"/>
+      <c r="AA5" s="69"/>
+      <c r="AB5" s="69"/>
+      <c r="AC5" s="69"/>
+      <c r="AD5" s="69"/>
+      <c r="AE5" s="69"/>
+      <c r="AF5" s="69"/>
+      <c r="AG5" s="69"/>
+      <c r="AH5" s="69"/>
+      <c r="AI5" s="69"/>
+      <c r="AJ5" s="69"/>
+      <c r="AK5" s="69"/>
+      <c r="AL5" s="69"/>
+      <c r="AM5" s="69"/>
+      <c r="AN5" s="69"/>
+      <c r="AO5" s="69"/>
+      <c r="AP5" s="69"/>
+      <c r="AQ5" s="69"/>
+      <c r="AR5" s="69"/>
+      <c r="AS5" s="69"/>
+      <c r="AT5" s="69"/>
+      <c r="AU5" s="69"/>
+      <c r="AV5" s="69"/>
+      <c r="AW5" s="69"/>
       <c r="BE5" t="s">
         <v>112</v>
       </c>
-      <c r="BF5" s="72" t="s">
+      <c r="BF5" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="BG5" s="77">
+      <c r="BG5" s="75">
         <v>0.35</v>
       </c>
-      <c r="BH5" s="77">
+      <c r="BH5" s="75">
         <v>0.25</v>
       </c>
-      <c r="BI5" s="77">
+      <c r="BI5" s="75">
         <v>0.45</v>
       </c>
-      <c r="BJ5" s="77">
+      <c r="BJ5" s="75">
         <v>0.4</v>
       </c>
-      <c r="BK5" s="77">
+      <c r="BK5" s="75">
         <v>0.45</v>
       </c>
-      <c r="BL5" s="78">
+      <c r="BL5" s="76">
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:64" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="117" t="s">
+    <row r="6" spans="1:64" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="115" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="88">
+      <c r="B6" s="86">
         <f t="shared" ref="B6:I6" si="0">IF(B3&lt;$BG$4,0,-(MIN(1,MAX(0,((B3-$BG$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BG$18)))^2)+2*MIN(1,MAX(0,((B3-$BG$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BG$18))))</f>
         <v>0</v>
       </c>
-      <c r="C6" s="88">
+      <c r="C6" s="86">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D6" s="88">
+      <c r="D6" s="86">
         <f t="shared" si="0"/>
         <v>0.39160000000000006</v>
       </c>
-      <c r="E6" s="88">
+      <c r="E6" s="86">
         <f t="shared" si="0"/>
         <v>0.68640000000000012</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="86">
         <f t="shared" si="0"/>
         <v>0.88440000000000007</v>
       </c>
-      <c r="G6" s="88">
+      <c r="G6" s="86">
         <f t="shared" si="0"/>
         <v>0.98560000000000003</v>
       </c>
-      <c r="H6" s="88">
+      <c r="H6" s="86">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I6" s="88">
+      <c r="I6" s="86">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="86">
         <f t="shared" ref="J6:Q6" si="1">IF(J3&lt;$BH$4,0,-(MIN(1,MAX(0,((J3-$BH$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BH$18)))^2)+2*MIN(1,MAX(0,((J3-$BH$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BH$18))))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="88">
+      <c r="K6" s="86">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L6" s="88">
+      <c r="L6" s="86">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M6" s="88">
+      <c r="M6" s="86">
         <f t="shared" si="1"/>
         <v>0.47437500000000005</v>
       </c>
-      <c r="N6" s="88">
+      <c r="N6" s="86">
         <f t="shared" si="1"/>
         <v>0.7975000000000001</v>
       </c>
-      <c r="O6" s="88">
+      <c r="O6" s="86">
         <f t="shared" si="1"/>
         <v>0.96937499999999999</v>
       </c>
-      <c r="P6" s="88">
+      <c r="P6" s="86">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="88">
+      <c r="Q6" s="86">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R6" s="88">
+      <c r="R6" s="86">
         <f t="shared" ref="R6:Y6" si="2">IF(R3&lt;$BI$4,0,-(MIN(1,MAX(0,((R3-$BI$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BI$18)))^2)+2*MIN(1,MAX(0,((R3-$BI$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BI$18))))</f>
         <v>0</v>
       </c>
-      <c r="S6" s="88">
+      <c r="S6" s="86">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T6" s="88">
+      <c r="T6" s="86">
         <f t="shared" si="2"/>
         <v>0.59888888888888892</v>
       </c>
-      <c r="U6" s="88">
+      <c r="U6" s="86">
         <f t="shared" si="2"/>
         <v>0.92888888888888888</v>
       </c>
-      <c r="V6" s="88">
+      <c r="V6" s="86">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="W6" s="88">
+      <c r="W6" s="86">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="X6" s="88">
+      <c r="X6" s="86">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Y6" s="88">
+      <c r="Y6" s="86">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Z6" s="88">
+      <c r="Z6" s="86">
         <f t="shared" ref="Z6:AG6" si="3">IF(Z3&lt;$BJ$4,0,-(MIN(1,MAX(0,((Z3-$BJ$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BJ$18)))^2)+2*MIN(1,MAX(0,((Z3-$BJ$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BJ$18))))</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="88">
+      <c r="AA6" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB6" s="88">
+      <c r="AB6" s="86">
         <f t="shared" si="3"/>
         <v>0.59888888888888892</v>
       </c>
-      <c r="AC6" s="88">
+      <c r="AC6" s="86">
         <f t="shared" si="3"/>
         <v>0.92888888888888888</v>
       </c>
-      <c r="AD6" s="88">
+      <c r="AD6" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AE6" s="88">
+      <c r="AE6" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AF6" s="88">
+      <c r="AF6" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AG6" s="88">
+      <c r="AG6" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AH6" s="88">
+      <c r="AH6" s="86">
         <f t="shared" ref="AH6:AO6" si="4">IF(AH3&lt;$BK$4,0,-(MIN(1,MAX(0,((AH3-$BK$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BK$18)))^2)+2*MIN(1,MAX(0,((AH3-$BK$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BK$18))))</f>
         <v>0</v>
       </c>
-      <c r="AI6" s="88">
+      <c r="AI6" s="86">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ6" s="88">
+      <c r="AJ6" s="86">
         <f t="shared" si="4"/>
         <v>0.47437500000000005</v>
       </c>
-      <c r="AK6" s="88">
+      <c r="AK6" s="86">
         <f t="shared" si="4"/>
         <v>0.7975000000000001</v>
       </c>
-      <c r="AL6" s="88">
+      <c r="AL6" s="86">
         <f t="shared" si="4"/>
         <v>0.96937499999999999</v>
       </c>
-      <c r="AM6" s="88">
+      <c r="AM6" s="86">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AN6" s="88">
+      <c r="AN6" s="86">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AO6" s="88">
+      <c r="AO6" s="86">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AP6" s="88">
+      <c r="AP6" s="86">
         <f t="shared" ref="AP6:AW6" si="5">IF(AP3&lt;$BL$4,0,-(MIN(1,MAX(0,((AP3-$BL$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BL$18)))^2)+2*MIN(1,MAX(0,((AP3-$BL$4+1)*_xlfn.XLOOKUP(Scenario,$AY$7:$AY$9,$BA$7:$BA$9,1,0)/$BL$18))))</f>
         <v>0</v>
       </c>
-      <c r="AQ6" s="88">
+      <c r="AQ6" s="86">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AR6" s="88">
+      <c r="AR6" s="86">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AS6" s="88">
+      <c r="AS6" s="86">
         <f t="shared" si="5"/>
         <v>0.7975000000000001</v>
       </c>
-      <c r="AT6" s="88">
+      <c r="AT6" s="86">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AU6" s="88">
+      <c r="AU6" s="86">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AV6" s="88">
+      <c r="AV6" s="86">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AW6" s="88">
+      <c r="AW6" s="86">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AX6"/>
-      <c r="AY6" s="98"/>
-      <c r="AZ6" s="99" t="s">
+      <c r="AY6" s="96"/>
+      <c r="AZ6" s="97" t="s">
         <v>110</v>
       </c>
-      <c r="BA6" s="99" t="s">
+      <c r="BA6" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="BB6" s="99" t="s">
+      <c r="BB6" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="BC6" s="100" t="s">
+      <c r="BC6" s="98" t="s">
         <v>109</v>
       </c>
       <c r="BD6"/>
       <c r="BE6" t="s">
         <v>112</v>
       </c>
-      <c r="BF6" s="72" t="s">
+      <c r="BF6" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="BG6" s="77">
+      <c r="BG6" s="75">
         <v>0.65</v>
       </c>
-      <c r="BH6" s="77">
+      <c r="BH6" s="75">
         <v>0.55000000000000004</v>
       </c>
-      <c r="BI6" s="77">
+      <c r="BI6" s="75">
         <v>0.7</v>
       </c>
-      <c r="BJ6" s="77">
+      <c r="BJ6" s="75">
         <v>0.7</v>
       </c>
-      <c r="BK6" s="77">
+      <c r="BK6" s="75">
         <v>0.6</v>
       </c>
-      <c r="BL6" s="78">
+      <c r="BL6" s="76">
         <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B7" s="69">
         <f>B4*(B6-B1)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="69">
         <f>C4*(C6-B6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="69">
         <f>D4*(D6-C6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>138.20734809220224</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="69">
         <f>E4*(E6-D6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>104.53273950664926</v>
       </c>
-      <c r="F7" s="71">
+      <c r="F7" s="69">
         <f>F4*(F6-E6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>70.538536600072717</v>
       </c>
-      <c r="G7" s="71">
+      <c r="G7" s="69">
         <f>G4*(G6-F6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>36.222479057958665</v>
       </c>
-      <c r="H7" s="71">
+      <c r="H7" s="69">
         <f>H4*(H6-G6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>5.1784114211190371</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="69">
         <f>I4*(I6-H6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="69">
         <f>J4*(J6-J1)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="69">
         <f>K4*(K6-J6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="69">
         <f>L4*(L6-K6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="69">
         <f>M4*(M6-L6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>126.15599975440992</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="69">
         <f>N4*(N6-M6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>86.336229692797332</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="69">
         <f>O4*(O6-N6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>46.139367006570964</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="69">
         <f>P4*(P6-O6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>8.259835925613066</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="69">
         <f>Q4*(Q6-P6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="69">
         <f>R4*(R6-R1)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="69">
         <f>S4*(S6-R6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="T7" s="71">
+      <c r="T7" s="69">
         <f>T4*(T6-S6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>244.89278261978745</v>
       </c>
-      <c r="U7" s="71">
+      <c r="U7" s="69">
         <f>U4*(U6-T6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>135.57514336425942</v>
       </c>
-      <c r="V7" s="71">
+      <c r="V7" s="69">
         <f>V4*(V6-U6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>29.352155482951428</v>
       </c>
-      <c r="W7" s="71">
+      <c r="W7" s="69">
         <f>W4*(W6-V6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="X7" s="71">
+      <c r="X7" s="69">
         <f>X4*(X6-W6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="71">
+      <c r="Y7" s="69">
         <f>Y4*(Y6-X6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="71">
+      <c r="Z7" s="69">
         <f>Z4*(Z6-Z1)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="71">
+      <c r="AA7" s="69">
         <f>AA4*(AA6-Z6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="71">
+      <c r="AB7" s="69">
         <f>AB4*(AB6-AA6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>306.11597827473435</v>
       </c>
-      <c r="AC7" s="71">
+      <c r="AC7" s="69">
         <f>AC4*(AC6-AB6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>169.46892920532429</v>
       </c>
-      <c r="AD7" s="71">
+      <c r="AD7" s="69">
         <f>AD4*(AD6-AC6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>36.690194353689293</v>
       </c>
-      <c r="AE7" s="71">
+      <c r="AE7" s="69">
         <f>AE4*(AE6-AD6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="71">
+      <c r="AF7" s="69">
         <f>AF4*(AF6-AE6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="71">
+      <c r="AG7" s="69">
         <f>AG4*(AG6-AF6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="71">
+      <c r="AH7" s="69">
         <f>AH4*(AH6-AH1)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="71">
+      <c r="AI7" s="69">
         <f>AI4*(AI6-AH6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ7" s="71">
+      <c r="AJ7" s="69">
         <f>AJ4*(AJ6-AI6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>105.12891733120105</v>
       </c>
-      <c r="AK7" s="71">
+      <c r="AK7" s="69">
         <f>AK4*(AK6-AJ6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>71.946117281230613</v>
       </c>
-      <c r="AL7" s="71">
+      <c r="AL7" s="69">
         <f>AL4*(AL6-AK6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>38.449076613006561</v>
       </c>
-      <c r="AM7" s="71">
+      <c r="AM7" s="69">
         <f>AM4*(AM6-AL6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>6.8831257322956336</v>
       </c>
-      <c r="AN7" s="71">
+      <c r="AN7" s="69">
         <f>AN4*(AN6-AM6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="71">
+      <c r="AO7" s="69">
         <f>AO4*(AO6-AN6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AP7" s="71">
+      <c r="AP7" s="69">
         <f>AP4*(AP6-AP1)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ7" s="71">
+      <c r="AQ7" s="69">
         <f>AQ4*(AQ6-AP6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="71">
+      <c r="AR7" s="69">
         <f>AR4*(AR6-AQ6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AS7" s="71">
+      <c r="AS7" s="69">
         <f>AS4*(AS6-AR6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>355.13828104777667</v>
       </c>
-      <c r="AT7" s="71">
+      <c r="AT7" s="69">
         <f>AT4*(AT6-AS6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>90.600005982648227</v>
       </c>
-      <c r="AU7" s="71">
+      <c r="AU7" s="69">
         <f>AU4*(AU6-AT6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AV7" s="71">
+      <c r="AV7" s="69">
         <f>AV4*(AV6-AU6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AW7" s="71">
+      <c r="AW7" s="69">
         <f>AW4*(AW6-AV6)*_xlfn.XLOOKUP(A1,AY7:AY9,AZ7:AZ9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AY7" s="101" t="s">
+      <c r="AY7" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="AZ7" s="90">
+      <c r="AZ7" s="88">
         <v>0.8</v>
       </c>
-      <c r="BA7" s="68">
+      <c r="BA7" s="66">
         <v>0.9</v>
       </c>
-      <c r="BB7" s="89">
+      <c r="BB7" s="87">
         <v>0.75</v>
       </c>
-      <c r="BC7" s="102">
+      <c r="BC7" s="100">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="BE7" s="71" t="s">
+      <c r="BE7" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="BF7" s="72" t="s">
+      <c r="BF7" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="BG7" s="77">
+      <c r="BG7" s="75">
         <v>0.85</v>
       </c>
-      <c r="BH7" s="77">
+      <c r="BH7" s="75">
         <v>0.75</v>
       </c>
-      <c r="BI7" s="77">
+      <c r="BI7" s="75">
         <v>0.85</v>
       </c>
-      <c r="BJ7" s="77">
+      <c r="BJ7" s="75">
         <v>0.85</v>
       </c>
-      <c r="BK7" s="77">
+      <c r="BK7" s="75">
         <v>0.75</v>
       </c>
-      <c r="BL7" s="78">
+      <c r="BL7" s="76">
         <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="71">
+      <c r="B8" s="69">
         <f>B1*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="69">
         <f>(B7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+B8</f>
         <v>0</v>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="69">
         <f>(C7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+C8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="71">
+      <c r="E8" s="69">
         <f>(D7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+D8</f>
         <v>131.29698068759211</v>
       </c>
-      <c r="F8" s="71">
+      <c r="F8" s="69">
         <f>(E7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+E8</f>
         <v>230.60308321890892</v>
       </c>
-      <c r="G8" s="71">
+      <c r="G8" s="69">
         <f>(F7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+F8</f>
         <v>297.61469298897799</v>
       </c>
-      <c r="H8" s="71">
+      <c r="H8" s="69">
         <f>(G7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+G8</f>
         <v>332.02604809403874</v>
       </c>
-      <c r="I8" s="71">
+      <c r="I8" s="69">
         <f>(H7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+H8</f>
         <v>336.94553894410183</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="69">
         <f>J1*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="69">
         <f>(J7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+J8</f>
         <v>0</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="69">
         <f>(K7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+K8</f>
         <v>0</v>
       </c>
-      <c r="M8" s="71">
+      <c r="M8" s="69">
         <f>(L7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+L8</f>
         <v>0</v>
       </c>
-      <c r="N8" s="71">
+      <c r="N8" s="69">
         <f>(M7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+M8</f>
         <v>119.84819976668942</v>
       </c>
-      <c r="O8" s="71">
+      <c r="O8" s="69">
         <f>(N7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+N8</f>
         <v>201.86761797484689</v>
       </c>
-      <c r="P8" s="71">
+      <c r="P8" s="69">
         <f>(O7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+O8</f>
         <v>245.70001663108931</v>
       </c>
-      <c r="Q8" s="71">
+      <c r="Q8" s="69">
         <f>(P7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+P8</f>
         <v>253.54686076042174</v>
       </c>
-      <c r="R8" s="71">
+      <c r="R8" s="69">
         <f>R1*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0)</f>
         <v>0</v>
       </c>
-      <c r="S8" s="71">
+      <c r="S8" s="69">
         <f>(R7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+R8</f>
         <v>0</v>
       </c>
-      <c r="T8" s="71">
+      <c r="T8" s="69">
         <f>(S7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+S8</f>
         <v>0</v>
       </c>
-      <c r="U8" s="71">
+      <c r="U8" s="69">
         <f>(T7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+T8</f>
         <v>232.64814348879807</v>
       </c>
-      <c r="V8" s="71">
+      <c r="V8" s="69">
         <f>(U7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+U8</f>
         <v>361.4445296848445</v>
       </c>
-      <c r="W8" s="71">
+      <c r="W8" s="69">
         <f>(V7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+V8</f>
         <v>389.32907739364833</v>
       </c>
-      <c r="X8" s="71">
+      <c r="X8" s="69">
         <f>(W7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+W8</f>
         <v>389.32907739364833</v>
       </c>
-      <c r="Y8" s="71">
+      <c r="Y8" s="69">
         <f>(X7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+X8</f>
         <v>389.32907739364833</v>
       </c>
-      <c r="Z8" s="71">
+      <c r="Z8" s="69">
         <f>Z1*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="71">
+      <c r="AA8" s="69">
         <f>(Z7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+Z8</f>
         <v>0</v>
       </c>
-      <c r="AB8" s="71">
+      <c r="AB8" s="69">
         <f>(AA7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AA8</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="71">
+      <c r="AC8" s="69">
         <f>(AB7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AB8</f>
         <v>290.81017936099761</v>
       </c>
-      <c r="AD8" s="71">
+      <c r="AD8" s="69">
         <f>(AC7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AC8</f>
         <v>451.80566210605571</v>
       </c>
-      <c r="AE8" s="71">
+      <c r="AE8" s="69">
         <f>(AD7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AD8</f>
         <v>486.66134674206052</v>
       </c>
-      <c r="AF8" s="71">
+      <c r="AF8" s="69">
         <f>(AE7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AE8</f>
         <v>486.66134674206052</v>
       </c>
-      <c r="AG8" s="71">
+      <c r="AG8" s="69">
         <f>(AF7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AF8</f>
         <v>486.66134674206052</v>
       </c>
-      <c r="AH8" s="71">
+      <c r="AH8" s="69">
         <f>AH1*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AI8" s="71">
+      <c r="AI8" s="69">
         <f>(AH7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AH8</f>
         <v>0</v>
       </c>
-      <c r="AJ8" s="71">
+      <c r="AJ8" s="69">
         <f>(AI7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AI8</f>
         <v>0</v>
       </c>
-      <c r="AK8" s="71">
+      <c r="AK8" s="69">
         <f>(AJ7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AJ8</f>
         <v>99.872471464640995</v>
       </c>
-      <c r="AL8" s="71">
+      <c r="AL8" s="69">
         <f>(AK7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AK8</f>
         <v>168.22128288181005</v>
       </c>
-      <c r="AM8" s="71">
+      <c r="AM8" s="69">
         <f>(AL7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AL8</f>
         <v>204.7479056641663</v>
       </c>
-      <c r="AN8" s="71">
+      <c r="AN8" s="69">
         <f>(AM7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AM8</f>
         <v>211.28687510984716</v>
       </c>
-      <c r="AO8" s="71">
+      <c r="AO8" s="69">
         <f>(AN7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AN8</f>
         <v>211.28687510984716</v>
       </c>
-      <c r="AP8" s="71">
+      <c r="AP8" s="69">
         <f>AP1*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ8" s="71">
+      <c r="AQ8" s="69">
         <f>(AP7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AP8</f>
         <v>0</v>
       </c>
-      <c r="AR8" s="71">
+      <c r="AR8" s="69">
         <f>(AQ7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AQ8</f>
         <v>0</v>
       </c>
-      <c r="AS8" s="71">
+      <c r="AS8" s="69">
         <f>(AR7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AR8</f>
         <v>0</v>
       </c>
-      <c r="AT8" s="71">
+      <c r="AT8" s="69">
         <f>(AS7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AS8</f>
         <v>337.38136699538785</v>
       </c>
-      <c r="AU8" s="71">
+      <c r="AU8" s="69">
         <f>(AT7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AT8</f>
         <v>423.45137267890368</v>
       </c>
-      <c r="AV8" s="71">
+      <c r="AV8" s="69">
         <f>(AU7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AU8</f>
         <v>423.45137267890368</v>
       </c>
-      <c r="AW8" s="71">
+      <c r="AW8" s="69">
         <f>(AV7*_xlfn.XLOOKUP(A1,AY7:AY9,BB7:BB9,,0))+AV8</f>
         <v>423.45137267890368</v>
       </c>
-      <c r="AX8" s="71"/>
-      <c r="AY8" s="101" t="s">
+      <c r="AX8" s="69"/>
+      <c r="AY8" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="AZ8" s="90">
+      <c r="AZ8" s="88">
         <v>1</v>
       </c>
-      <c r="BA8" s="68">
+      <c r="BA8" s="66">
         <v>1</v>
       </c>
-      <c r="BB8" s="89">
+      <c r="BB8" s="87">
         <v>0.85</v>
       </c>
-      <c r="BC8" s="103">
+      <c r="BC8" s="101">
         <v>0.02</v>
       </c>
-      <c r="BF8" s="73" t="s">
+      <c r="BF8" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="BG8" s="77">
+      <c r="BG8" s="75">
         <v>0.02</v>
       </c>
-      <c r="BH8" s="77">
+      <c r="BH8" s="75">
         <v>0.03</v>
       </c>
-      <c r="BI8" s="77">
+      <c r="BI8" s="75">
         <v>0.02</v>
       </c>
-      <c r="BJ8" s="77">
+      <c r="BJ8" s="75">
         <v>0.02</v>
       </c>
-      <c r="BK8" s="77">
+      <c r="BK8" s="75">
         <v>0.01</v>
       </c>
-      <c r="BL8" s="78">
+      <c r="BL8" s="76">
         <v>0.01</v>
       </c>
     </row>
     <row r="9" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="74">
         <f>SUM(B6:B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="74">
         <f t="shared" ref="C9:AW9" si="6">SUM(C6:C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="76">
+      <c r="D9" s="74">
         <f t="shared" si="6"/>
         <v>138.59894809220225</v>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="74">
         <f t="shared" si="6"/>
         <v>236.51612019424138</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="74">
         <f t="shared" si="6"/>
         <v>302.02601981898164</v>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="74">
         <f t="shared" si="6"/>
         <v>334.82277204693668</v>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="74">
         <f t="shared" si="6"/>
         <v>338.20445951515779</v>
       </c>
-      <c r="I9" s="76">
+      <c r="I9" s="74">
         <f t="shared" si="6"/>
         <v>337.94553894410183</v>
       </c>
-      <c r="J9" s="76">
+      <c r="J9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L9" s="76">
+      <c r="L9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M9" s="76">
+      <c r="M9" s="74">
         <f t="shared" si="6"/>
         <v>126.63037475440991</v>
       </c>
-      <c r="N9" s="76">
+      <c r="N9" s="74">
         <f t="shared" si="6"/>
         <v>206.98192945948676</v>
       </c>
-      <c r="O9" s="76">
+      <c r="O9" s="74">
         <f t="shared" si="6"/>
         <v>248.97635998141786</v>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="74">
         <f t="shared" si="6"/>
         <v>254.95985255670237</v>
       </c>
-      <c r="Q9" s="76">
+      <c r="Q9" s="74">
         <f t="shared" si="6"/>
         <v>254.54686076042174</v>
       </c>
-      <c r="R9" s="76">
+      <c r="R9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S9" s="76">
+      <c r="S9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T9" s="76">
+      <c r="T9" s="74">
         <f t="shared" si="6"/>
         <v>245.49167150867635</v>
       </c>
-      <c r="U9" s="76">
+      <c r="U9" s="74">
         <f t="shared" si="6"/>
         <v>369.15217574194639</v>
       </c>
-      <c r="V9" s="76">
+      <c r="V9" s="74">
         <f t="shared" si="6"/>
         <v>391.79668516779594</v>
       </c>
-      <c r="W9" s="76">
+      <c r="W9" s="74">
         <f t="shared" si="6"/>
         <v>390.32907739364833</v>
       </c>
-      <c r="X9" s="76">
+      <c r="X9" s="74">
         <f t="shared" si="6"/>
         <v>390.32907739364833</v>
       </c>
-      <c r="Y9" s="76">
+      <c r="Y9" s="74">
         <f t="shared" si="6"/>
         <v>390.32907739364833</v>
       </c>
-      <c r="Z9" s="76">
+      <c r="Z9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA9" s="76">
+      <c r="AA9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB9" s="76">
+      <c r="AB9" s="74">
         <f t="shared" si="6"/>
         <v>306.71486716362324</v>
       </c>
-      <c r="AC9" s="76">
+      <c r="AC9" s="74">
         <f t="shared" si="6"/>
         <v>461.20799745521077</v>
       </c>
-      <c r="AD9" s="76">
+      <c r="AD9" s="74">
         <f t="shared" si="6"/>
         <v>489.49585645974503</v>
       </c>
-      <c r="AE9" s="76">
+      <c r="AE9" s="74">
         <f t="shared" si="6"/>
         <v>487.66134674206052</v>
       </c>
-      <c r="AF9" s="76">
+      <c r="AF9" s="74">
         <f t="shared" si="6"/>
         <v>487.66134674206052</v>
       </c>
-      <c r="AG9" s="76">
+      <c r="AG9" s="74">
         <f t="shared" si="6"/>
         <v>487.66134674206052</v>
       </c>
-      <c r="AH9" s="76">
+      <c r="AH9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI9" s="76">
+      <c r="AI9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AJ9" s="76">
+      <c r="AJ9" s="74">
         <f t="shared" si="6"/>
         <v>105.60329233120105</v>
       </c>
-      <c r="AK9" s="76">
+      <c r="AK9" s="74">
         <f t="shared" si="6"/>
         <v>172.61608874587159</v>
       </c>
-      <c r="AL9" s="76">
+      <c r="AL9" s="74">
         <f t="shared" si="6"/>
         <v>207.63973449481662</v>
       </c>
-      <c r="AM9" s="76">
+      <c r="AM9" s="74">
         <f t="shared" si="6"/>
         <v>212.63103139646194</v>
       </c>
-      <c r="AN9" s="76">
+      <c r="AN9" s="74">
         <f t="shared" si="6"/>
         <v>212.28687510984716</v>
       </c>
-      <c r="AO9" s="76">
+      <c r="AO9" s="74">
         <f t="shared" si="6"/>
         <v>212.28687510984716</v>
       </c>
-      <c r="AP9" s="76">
+      <c r="AP9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ9" s="76">
+      <c r="AQ9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AR9" s="76">
+      <c r="AR9" s="74">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AS9" s="76">
+      <c r="AS9" s="74">
         <f t="shared" si="6"/>
         <v>355.93578104777669</v>
       </c>
-      <c r="AT9" s="76">
+      <c r="AT9" s="74">
         <f t="shared" si="6"/>
         <v>428.98137297803606</v>
       </c>
-      <c r="AU9" s="76">
+      <c r="AU9" s="74">
         <f t="shared" si="6"/>
         <v>424.45137267890368</v>
       </c>
-      <c r="AV9" s="76">
+      <c r="AV9" s="74">
         <f t="shared" si="6"/>
         <v>424.45137267890368</v>
       </c>
-      <c r="AW9" s="76">
+      <c r="AW9" s="74">
         <f t="shared" si="6"/>
         <v>424.45137267890368</v>
       </c>
-      <c r="AY9" s="104" t="s">
+      <c r="AY9" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="AZ9" s="97">
+      <c r="AZ9" s="95">
         <v>1.2</v>
       </c>
-      <c r="BA9" s="69">
+      <c r="BA9" s="67">
         <v>1.1000000000000001</v>
       </c>
-      <c r="BB9" s="105">
+      <c r="BB9" s="103">
         <v>0.95</v>
       </c>
-      <c r="BC9" s="106">
+      <c r="BC9" s="104">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BF9" s="72" t="s">
+      <c r="BF9" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="BG9" s="77">
+      <c r="BG9" s="75">
         <v>0.24</v>
       </c>
-      <c r="BH9" s="77">
+      <c r="BH9" s="75">
         <v>0.26</v>
       </c>
-      <c r="BI9" s="77">
+      <c r="BI9" s="75">
         <v>0.2</v>
       </c>
-      <c r="BJ9" s="77">
+      <c r="BJ9" s="75">
         <v>0.16</v>
       </c>
-      <c r="BK9" s="77">
+      <c r="BK9" s="75">
         <v>0.24</v>
       </c>
-      <c r="BL9" s="78">
+      <c r="BL9" s="76">
         <v>0.23</v>
       </c>
     </row>
     <row r="10" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="113" t="s">
         <v>104</v>
       </c>
       <c r="B10" s="1">
@@ -5995,30 +6060,30 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BF10" s="72" t="s">
+      <c r="BF10" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="BG10" s="77">
+      <c r="BG10" s="75">
         <v>0.2</v>
       </c>
-      <c r="BH10" s="77">
+      <c r="BH10" s="75">
         <v>0.25</v>
       </c>
-      <c r="BI10" s="77">
+      <c r="BI10" s="75">
         <v>0.3</v>
       </c>
-      <c r="BJ10" s="77">
+      <c r="BJ10" s="75">
         <v>0.3</v>
       </c>
-      <c r="BK10" s="77">
+      <c r="BK10" s="75">
         <v>0.35</v>
       </c>
-      <c r="BL10" s="78">
+      <c r="BL10" s="76">
         <v>0.15</v>
       </c>
     </row>
     <row r="11" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A11" s="119" t="s">
+      <c r="A11" s="117" t="s">
         <v>96</v>
       </c>
       <c r="B11" s="1">
@@ -6214,36 +6279,36 @@
         <v>-49.024133544413381</v>
       </c>
       <c r="AX11" s="1"/>
-      <c r="AY11" s="96" t="s">
+      <c r="AY11" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="AZ11" s="96">
+      <c r="AZ11" s="94">
         <v>0.02</v>
       </c>
-      <c r="BF11" s="72" t="s">
+      <c r="BF11" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="BG11" s="77">
+      <c r="BG11" s="75">
         <v>0.8</v>
       </c>
-      <c r="BH11" s="77">
+      <c r="BH11" s="75">
         <v>0.75</v>
       </c>
-      <c r="BI11" s="77">
+      <c r="BI11" s="75">
         <v>0.7</v>
       </c>
-      <c r="BJ11" s="77">
+      <c r="BJ11" s="75">
         <v>0.7</v>
       </c>
-      <c r="BK11" s="77">
+      <c r="BK11" s="75">
         <v>0.65</v>
       </c>
-      <c r="BL11" s="78">
+      <c r="BL11" s="76">
         <v>0.85</v>
       </c>
     </row>
     <row r="12" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A12" s="115" t="s">
+      <c r="A12" s="113" t="s">
         <v>97</v>
       </c>
       <c r="B12" s="1">
@@ -6439,37 +6504,37 @@
         <v>-277.8034234183425</v>
       </c>
       <c r="AX12" s="1"/>
-      <c r="AY12" s="96" t="s">
+      <c r="AY12" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="AZ12" s="96">
+      <c r="AZ12" s="94">
         <f>SOTP!W2</f>
         <v>0.10567499999999999</v>
       </c>
-      <c r="BF12" s="72" t="s">
+      <c r="BF12" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="BG12" s="77">
+      <c r="BG12" s="75">
         <v>0.02</v>
       </c>
-      <c r="BH12" s="77">
+      <c r="BH12" s="75">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BI12" s="77">
+      <c r="BI12" s="75">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BJ12" s="77">
+      <c r="BJ12" s="75">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BK12" s="77">
+      <c r="BK12" s="75">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BL12" s="78">
+      <c r="BL12" s="76">
         <v>0.01</v>
       </c>
     </row>
     <row r="13" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="118" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="1">
@@ -6665,37 +6730,37 @@
         <v>97.623815716147817</v>
       </c>
       <c r="AX13" s="1"/>
-      <c r="AY13" s="96" t="s">
+      <c r="AY13" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="AZ13" s="96">
+      <c r="AZ13" s="94">
         <f>SOTP!W4</f>
         <v>5.7975388146743925E-2</v>
       </c>
-      <c r="BF13" s="72" t="s">
+      <c r="BF13" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="BG13" s="77">
+      <c r="BG13" s="75">
         <v>0.08</v>
       </c>
-      <c r="BH13" s="77">
+      <c r="BH13" s="75">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BI13" s="77">
+      <c r="BI13" s="75">
         <v>0.06</v>
       </c>
-      <c r="BJ13" s="77">
+      <c r="BJ13" s="75">
         <v>0.06</v>
       </c>
-      <c r="BK13" s="77">
+      <c r="BK13" s="75">
         <v>0.06</v>
       </c>
-      <c r="BL13" s="78">
+      <c r="BL13" s="76">
         <v>0.06</v>
       </c>
     </row>
     <row r="14" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="113" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="1">
@@ -6891,30 +6956,30 @@
         <v>10.316396725803919</v>
       </c>
       <c r="AX14" s="1"/>
-      <c r="BF14" s="72" t="s">
+      <c r="BF14" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="BG14" s="77">
+      <c r="BG14" s="75">
         <v>0.04</v>
       </c>
-      <c r="BH14" s="77">
+      <c r="BH14" s="75">
         <v>0.03</v>
       </c>
-      <c r="BI14" s="77">
+      <c r="BI14" s="75">
         <v>0.02</v>
       </c>
-      <c r="BJ14" s="79">
+      <c r="BJ14" s="77">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="BK14" s="79">
+      <c r="BK14" s="77">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BL14" s="80">
+      <c r="BL14" s="78">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A15" s="120" t="s">
+      <c r="A15" s="118" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="1">
@@ -7110,30 +7175,30 @@
         <v>107.94021244195173</v>
       </c>
       <c r="AX15" s="1"/>
-      <c r="BF15" s="72" t="s">
+      <c r="BF15" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="BG15" s="77">
+      <c r="BG15" s="75">
         <v>0.02</v>
       </c>
-      <c r="BH15" s="79">
+      <c r="BH15" s="77">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BI15" s="77">
+      <c r="BI15" s="75">
         <v>0.01</v>
       </c>
-      <c r="BJ15" s="79">
+      <c r="BJ15" s="77">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BK15" s="79">
+      <c r="BK15" s="77">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BL15" s="78">
+      <c r="BL15" s="76">
         <v>0.01</v>
       </c>
     </row>
     <row r="16" spans="1:64" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="115" t="s">
+      <c r="A16" s="113" t="s">
         <v>105</v>
       </c>
       <c r="B16" s="1">
@@ -7163,7 +7228,7 @@
         <f t="shared" si="28"/>
         <v>-0.27053499745768933</v>
       </c>
-      <c r="I16" s="92">
+      <c r="I16" s="90">
         <f t="shared" si="28"/>
         <v>2.0713645684477342E-2</v>
       </c>
@@ -7194,7 +7259,7 @@
         <f t="shared" si="29"/>
         <v>-0.41884448026991611</v>
       </c>
-      <c r="Q16" s="92">
+      <c r="Q16" s="90">
         <f t="shared" si="29"/>
         <v>2.8909425739644522E-2</v>
       </c>
@@ -7217,7 +7282,7 @@
         <f t="shared" si="30"/>
         <v>-1.3586705655509728</v>
       </c>
-      <c r="W16" s="92">
+      <c r="W16" s="90">
         <f t="shared" si="30"/>
         <v>8.8056466448856549E-2</v>
       </c>
@@ -7248,7 +7313,7 @@
         <f t="shared" si="31"/>
         <v>-1.6972715402720553</v>
       </c>
-      <c r="AE16" s="92">
+      <c r="AE16" s="90">
         <f t="shared" si="31"/>
         <v>0.11007058306107069</v>
       </c>
@@ -7279,11 +7344,11 @@
         <f t="shared" si="32"/>
         <v>-2.1014187449367014</v>
       </c>
-      <c r="AM16" s="92">
+      <c r="AM16" s="90">
         <f t="shared" si="32"/>
         <v>-0.29947781409871876</v>
       </c>
-      <c r="AN16" s="92">
+      <c r="AN16" s="90">
         <f t="shared" si="32"/>
         <v>2.0649377196886576E-2</v>
       </c>
@@ -7323,32 +7388,32 @@
         <v>0</v>
       </c>
       <c r="AX16" s="1"/>
-      <c r="AZ16" s="91"/>
+      <c r="AZ16" s="89"/>
       <c r="BE16"/>
-      <c r="BF16" s="72" t="s">
+      <c r="BF16" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="BG16" s="77">
+      <c r="BG16" s="75">
         <v>0.04</v>
       </c>
-      <c r="BH16" s="77">
+      <c r="BH16" s="75">
         <v>0.03</v>
       </c>
-      <c r="BI16" s="77">
+      <c r="BI16" s="75">
         <v>0.02</v>
       </c>
-      <c r="BJ16" s="79">
+      <c r="BJ16" s="77">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="BK16" s="79">
+      <c r="BK16" s="77">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="BL16" s="78">
+      <c r="BL16" s="76">
         <v>0.03</v>
       </c>
     </row>
     <row r="17" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="113" t="s">
         <v>108</v>
       </c>
       <c r="B17" s="1">
@@ -7545,36 +7610,36 @@
       </c>
       <c r="AX17" s="1"/>
       <c r="BE17" s="3"/>
-      <c r="BF17" s="72" t="s">
+      <c r="BF17" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="BG17" s="71">
+      <c r="BG17" s="69">
         <f>BG16*SOTP!B38</f>
         <v>290</v>
       </c>
-      <c r="BH17" s="71">
+      <c r="BH17" s="69">
         <f>BH16*SOTP!B38</f>
         <v>217.5</v>
       </c>
-      <c r="BI17" s="71">
+      <c r="BI17" s="69">
         <f>BI16*SOTP!H38</f>
         <v>336</v>
       </c>
-      <c r="BJ17" s="71">
+      <c r="BJ17" s="69">
         <f>BJ16*SOTP!H38</f>
         <v>420</v>
       </c>
-      <c r="BK17" s="71">
+      <c r="BK17" s="69">
         <f>BK16*SOTP!N38</f>
         <v>182.1</v>
       </c>
-      <c r="BL17" s="75">
+      <c r="BL17" s="73">
         <f>BL16*SOTP!N38</f>
         <v>364.2</v>
       </c>
     </row>
     <row r="18" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A18" s="121" t="s">
+      <c r="A18" s="119" t="s">
         <v>4</v>
       </c>
       <c r="B18" s="1">
@@ -7764,31 +7829,31 @@
         <v>4.2445137267890365</v>
       </c>
       <c r="AX18" s="1"/>
-      <c r="AY18" s="71"/>
-      <c r="BF18" s="74" t="s">
+      <c r="AY18" s="69"/>
+      <c r="BF18" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="BG18" s="81">
+      <c r="BG18" s="79">
         <v>5</v>
       </c>
-      <c r="BH18" s="81">
+      <c r="BH18" s="79">
         <v>4</v>
       </c>
-      <c r="BI18" s="81">
+      <c r="BI18" s="79">
         <v>3</v>
       </c>
-      <c r="BJ18" s="81">
+      <c r="BJ18" s="79">
         <v>3</v>
       </c>
-      <c r="BK18" s="81">
+      <c r="BK18" s="79">
         <v>4</v>
       </c>
-      <c r="BL18" s="82">
+      <c r="BL18" s="80">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A19" s="120" t="s">
+      <c r="A19" s="118" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="5">
@@ -7984,36 +8049,36 @@
         <v>107.94021244195173</v>
       </c>
       <c r="AX19" s="1"/>
-      <c r="AY19" s="71"/>
-      <c r="AZ19" s="71"/>
-      <c r="BA19" s="71"/>
-      <c r="BB19" s="71"/>
-      <c r="BC19" s="71"/>
-      <c r="BD19" s="71"/>
-      <c r="BE19" s="71"/>
-      <c r="BF19" s="71"/>
-      <c r="BG19" s="71"/>
-      <c r="BH19" s="71"/>
-      <c r="BI19" s="71"/>
-    </row>
-    <row r="20" spans="1:64" s="93" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="121"/>
+      <c r="AY19" s="69"/>
+      <c r="AZ19" s="69"/>
+      <c r="BA19" s="69"/>
+      <c r="BB19" s="69"/>
+      <c r="BC19" s="69"/>
+      <c r="BD19" s="69"/>
+      <c r="BE19" s="69"/>
+      <c r="BF19" s="69"/>
+      <c r="BG19" s="69"/>
+      <c r="BH19" s="69"/>
+      <c r="BI19" s="69"/>
+    </row>
+    <row r="20" spans="1:64" s="91" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="119"/>
       <c r="AX20" s="1"/>
-      <c r="AY20" s="71"/>
-      <c r="AZ20" s="71"/>
-      <c r="BA20" s="71"/>
-      <c r="BB20" s="71"/>
-      <c r="BC20" s="71"/>
-      <c r="BD20" s="71"/>
-      <c r="BE20" s="71"/>
-      <c r="BF20" s="94"/>
-      <c r="BG20" s="94"/>
-      <c r="BH20" s="94"/>
-      <c r="BI20" s="94"/>
+      <c r="AY20" s="69"/>
+      <c r="AZ20" s="69"/>
+      <c r="BA20" s="69"/>
+      <c r="BB20" s="69"/>
+      <c r="BC20" s="69"/>
+      <c r="BD20" s="69"/>
+      <c r="BE20" s="69"/>
+      <c r="BF20" s="92"/>
+      <c r="BG20" s="92"/>
+      <c r="BH20" s="92"/>
+      <c r="BI20" s="92"/>
       <c r="BJ20"/>
     </row>
     <row r="21" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="117" t="s">
         <v>113</v>
       </c>
       <c r="B21" s="1">
@@ -8209,20 +8274,20 @@
         <v>32.382063732585515</v>
       </c>
       <c r="AX21" s="1"/>
-      <c r="AY21" s="71"/>
-      <c r="AZ21" s="71"/>
-      <c r="BA21" s="71"/>
-      <c r="BB21" s="71"/>
-      <c r="BC21" s="71"/>
-      <c r="BD21" s="71"/>
-      <c r="BE21" s="71"/>
-      <c r="BF21" s="71"/>
-      <c r="BG21" s="71"/>
-      <c r="BH21" s="71"/>
-      <c r="BI21" s="71"/>
+      <c r="AY21" s="69"/>
+      <c r="AZ21" s="69"/>
+      <c r="BA21" s="69"/>
+      <c r="BB21" s="69"/>
+      <c r="BC21" s="69"/>
+      <c r="BD21" s="69"/>
+      <c r="BE21" s="69"/>
+      <c r="BF21" s="69"/>
+      <c r="BG21" s="69"/>
+      <c r="BH21" s="69"/>
+      <c r="BI21" s="69"/>
     </row>
     <row r="22" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A22" s="119" t="s">
+      <c r="A22" s="117" t="s">
         <v>114</v>
       </c>
       <c r="B22" s="1">
@@ -8418,20 +8483,20 @@
         <v>20.630036918935545</v>
       </c>
       <c r="AX22" s="1"/>
-      <c r="AY22" s="71"/>
-      <c r="AZ22" s="71"/>
-      <c r="BA22" s="71"/>
-      <c r="BB22" s="71"/>
-      <c r="BC22" s="71"/>
-      <c r="BD22" s="71"/>
-      <c r="BE22" s="71"/>
-      <c r="BF22" s="71"/>
-      <c r="BG22" s="71"/>
-      <c r="BH22" s="71"/>
-      <c r="BI22" s="71"/>
+      <c r="AY22" s="69"/>
+      <c r="AZ22" s="69"/>
+      <c r="BA22" s="69"/>
+      <c r="BB22" s="69"/>
+      <c r="BC22" s="69"/>
+      <c r="BD22" s="69"/>
+      <c r="BE22" s="69"/>
+      <c r="BF22" s="69"/>
+      <c r="BG22" s="69"/>
+      <c r="BH22" s="69"/>
+      <c r="BI22" s="69"/>
     </row>
     <row r="23" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="117" t="s">
         <v>119</v>
       </c>
       <c r="B23" s="1">
@@ -8501,20 +8566,20 @@
       <c r="AV23" s="1"/>
       <c r="AW23" s="1"/>
       <c r="AX23" s="1"/>
-      <c r="AY23" s="71"/>
-      <c r="AZ23" s="71"/>
-      <c r="BA23" s="71"/>
-      <c r="BB23" s="71"/>
-      <c r="BC23" s="71"/>
-      <c r="BD23" s="71"/>
-      <c r="BE23" s="71"/>
-      <c r="BF23" s="71"/>
-      <c r="BG23" s="71"/>
-      <c r="BH23" s="71"/>
-      <c r="BI23" s="71"/>
+      <c r="AY23" s="69"/>
+      <c r="AZ23" s="69"/>
+      <c r="BA23" s="69"/>
+      <c r="BB23" s="69"/>
+      <c r="BC23" s="69"/>
+      <c r="BD23" s="69"/>
+      <c r="BE23" s="69"/>
+      <c r="BF23" s="69"/>
+      <c r="BG23" s="69"/>
+      <c r="BH23" s="69"/>
+      <c r="BI23" s="69"/>
     </row>
     <row r="24" spans="1:64" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="122" t="s">
+      <c r="A24" s="120" t="s">
         <v>120</v>
       </c>
       <c r="B24" s="5">
@@ -8543,7 +8608,7 @@
       </c>
     </row>
     <row r="25" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A25" s="119"/>
+      <c r="A25" s="117"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -8593,20 +8658,20 @@
       <c r="AV25" s="1"/>
       <c r="AW25" s="1"/>
       <c r="AX25" s="1"/>
-      <c r="AY25" s="71"/>
-      <c r="AZ25" s="71"/>
-      <c r="BA25" s="71"/>
-      <c r="BB25" s="71"/>
-      <c r="BC25" s="71"/>
-      <c r="BD25" s="71"/>
-      <c r="BE25" s="71"/>
-      <c r="BF25" s="71"/>
-      <c r="BG25" s="71"/>
-      <c r="BH25" s="71"/>
-      <c r="BI25" s="71"/>
-    </row>
-    <row r="26" spans="1:64" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="119" t="s">
+      <c r="AY25" s="69"/>
+      <c r="AZ25" s="69"/>
+      <c r="BA25" s="69"/>
+      <c r="BB25" s="69"/>
+      <c r="BC25" s="69"/>
+      <c r="BD25" s="69"/>
+      <c r="BE25" s="69"/>
+      <c r="BF25" s="69"/>
+      <c r="BG25" s="69"/>
+      <c r="BH25" s="69"/>
+      <c r="BI25" s="69"/>
+    </row>
+    <row r="26" spans="1:64" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="117" t="s">
         <v>115</v>
       </c>
       <c r="B26" s="1">
@@ -8804,8 +8869,8 @@
       <c r="AX26" s="1"/>
       <c r="BJ26"/>
     </row>
-    <row r="27" spans="1:64" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="119" t="s">
+    <row r="27" spans="1:64" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="117" t="s">
         <v>116</v>
       </c>
       <c r="B27" s="1">
@@ -9003,8 +9068,8 @@
       <c r="AX27" s="1"/>
       <c r="BJ27"/>
     </row>
-    <row r="28" spans="1:64" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="119" t="s">
+    <row r="28" spans="1:64" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="117" t="s">
         <v>119</v>
       </c>
       <c r="B28" s="1">
@@ -9034,7 +9099,7 @@
       <c r="AX28" s="1"/>
     </row>
     <row r="29" spans="1:64" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="122" t="s">
+      <c r="A29" s="120" t="s">
         <v>121</v>
       </c>
       <c r="B29" s="5">
@@ -9062,12 +9127,12 @@
         <v>1292.3506172018872</v>
       </c>
     </row>
-    <row r="30" spans="1:64" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="119"/>
+    <row r="30" spans="1:64" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="117"/>
       <c r="AX30" s="1"/>
     </row>
-    <row r="31" spans="1:64" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="115" t="s">
+    <row r="31" spans="1:64" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="113" t="s">
         <v>117</v>
       </c>
       <c r="B31" s="1">
@@ -9265,7 +9330,7 @@
       <c r="AX31" s="1"/>
     </row>
     <row r="32" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A32" s="119" t="s">
+      <c r="A32" s="117" t="s">
         <v>118</v>
       </c>
       <c r="B32" s="1">
@@ -9461,14 +9526,14 @@
         <v>55.013431783828132</v>
       </c>
       <c r="AX32" s="1"/>
-      <c r="BE32" s="95"/>
-      <c r="BF32" s="95"/>
-      <c r="BG32" s="95"/>
-      <c r="BH32" s="95"/>
-      <c r="BI32" s="95"/>
-    </row>
-    <row r="33" spans="1:61" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="119" t="s">
+      <c r="BE32" s="93"/>
+      <c r="BF32" s="93"/>
+      <c r="BG32" s="93"/>
+      <c r="BH32" s="93"/>
+      <c r="BI32" s="93"/>
+    </row>
+    <row r="33" spans="1:61" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="117" t="s">
         <v>119</v>
       </c>
       <c r="B33" s="1">
@@ -9540,7 +9605,7 @@
       <c r="AX33" s="1"/>
     </row>
     <row r="34" spans="1:61" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="122" t="s">
+      <c r="A34" s="120" t="s">
         <v>122</v>
       </c>
       <c r="B34" s="5">
@@ -9569,7 +9634,7 @@
       </c>
     </row>
     <row r="35" spans="1:61" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="120"/>
+      <c r="A35" s="118"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -9619,14 +9684,14 @@
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
       <c r="AX35" s="5"/>
-      <c r="BE35" s="76"/>
-      <c r="BF35" s="76"/>
-      <c r="BG35" s="76"/>
-      <c r="BH35" s="76"/>
-      <c r="BI35" s="76"/>
+      <c r="BE35" s="74"/>
+      <c r="BF35" s="74"/>
+      <c r="BG35" s="74"/>
+      <c r="BH35" s="74"/>
+      <c r="BI35" s="74"/>
     </row>
     <row r="36" spans="1:61" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="118" t="s">
+      <c r="A36" s="116" t="s">
         <v>123</v>
       </c>
       <c r="B36" s="5">
@@ -9696,14 +9761,14 @@
       <c r="AV36" s="5"/>
       <c r="AW36" s="5"/>
       <c r="AX36" s="5"/>
-      <c r="BE36" s="76"/>
-      <c r="BF36" s="76"/>
-      <c r="BG36" s="76"/>
-      <c r="BH36" s="76"/>
-      <c r="BI36" s="76"/>
-    </row>
-    <row r="37" spans="1:61" s="71" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="119"/>
+      <c r="BE36" s="74"/>
+      <c r="BF36" s="74"/>
+      <c r="BG36" s="74"/>
+      <c r="BH36" s="74"/>
+      <c r="BI36" s="74"/>
+    </row>
+    <row r="37" spans="1:61" s="69" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="117"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -9757,10 +9822,10 @@
       <c r="BD37"/>
     </row>
     <row r="38" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A38" s="123" t="s">
+      <c r="A38" s="121" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="112" t="s">
+      <c r="B38" s="110" t="s">
         <v>125</v>
       </c>
       <c r="G38" s="1"/>
@@ -9813,10 +9878,10 @@
       <c r="AX38" s="1"/>
     </row>
     <row r="39" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A39" s="123" t="s">
+      <c r="A39" s="121" t="s">
         <v>126</v>
       </c>
-      <c r="B39" s="112">
+      <c r="B39" s="110">
         <f>SOTP!H19</f>
         <v>9168.0634995460532</v>
       </c>
@@ -9872,10 +9937,10 @@
       <c r="AX39" s="1"/>
     </row>
     <row r="40" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A40" s="123" t="s">
+      <c r="A40" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="B40" s="112">
+      <c r="B40" s="110">
         <f>B36+J36</f>
         <v>1904.92721226189</v>
       </c>
@@ -9931,7 +9996,7 @@
       <c r="AX40" s="1"/>
     </row>
     <row r="41" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A41" s="120" t="s">
+      <c r="A41" s="118" t="s">
         <v>128</v>
       </c>
       <c r="B41" s="5">
@@ -9988,13 +10053,13 @@
       <c r="AV41" s="1"/>
       <c r="AW41" s="1"/>
       <c r="AX41" s="1"/>
-      <c r="BC41" s="71"/>
-      <c r="BD41" s="71"/>
-      <c r="BE41" s="71"/>
-      <c r="BF41" s="71"/>
-      <c r="BG41" s="71"/>
-      <c r="BH41" s="71"/>
-      <c r="BI41" s="71"/>
+      <c r="BC41" s="69"/>
+      <c r="BD41" s="69"/>
+      <c r="BE41" s="69"/>
+      <c r="BF41" s="69"/>
+      <c r="BG41" s="69"/>
+      <c r="BH41" s="69"/>
+      <c r="BI41" s="69"/>
     </row>
     <row r="42" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B42" s="1"/>
@@ -10042,13 +10107,13 @@
       <c r="AV42" s="1"/>
       <c r="AW42" s="1"/>
       <c r="AX42" s="1"/>
-      <c r="BC42" s="71"/>
-      <c r="BD42" s="71"/>
-      <c r="BE42" s="71"/>
-      <c r="BF42" s="71"/>
-      <c r="BG42" s="71"/>
-      <c r="BH42" s="71"/>
-      <c r="BI42" s="71"/>
+      <c r="BC42" s="69"/>
+      <c r="BD42" s="69"/>
+      <c r="BE42" s="69"/>
+      <c r="BF42" s="69"/>
+      <c r="BG42" s="69"/>
+      <c r="BH42" s="69"/>
+      <c r="BI42" s="69"/>
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B43" s="26">
@@ -10151,13 +10216,13 @@
       <c r="AV43" s="1"/>
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
-      <c r="BC43" s="71"/>
-      <c r="BD43" s="71"/>
-      <c r="BE43" s="71"/>
-      <c r="BF43" s="71"/>
-      <c r="BG43" s="71"/>
-      <c r="BH43" s="71"/>
-      <c r="BI43" s="71"/>
+      <c r="BC43" s="69"/>
+      <c r="BD43" s="69"/>
+      <c r="BE43" s="69"/>
+      <c r="BF43" s="69"/>
+      <c r="BG43" s="69"/>
+      <c r="BH43" s="69"/>
+      <c r="BI43" s="69"/>
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B44" s="25">
@@ -10251,13 +10316,13 @@
       <c r="AV44" s="1"/>
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
-      <c r="BC44" s="71"/>
-      <c r="BD44" s="71"/>
-      <c r="BE44" s="71"/>
-      <c r="BF44" s="71"/>
-      <c r="BG44" s="71"/>
-      <c r="BH44" s="71"/>
-      <c r="BI44" s="71"/>
+      <c r="BC44" s="69"/>
+      <c r="BD44" s="69"/>
+      <c r="BE44" s="69"/>
+      <c r="BF44" s="69"/>
+      <c r="BG44" s="69"/>
+      <c r="BH44" s="69"/>
+      <c r="BI44" s="69"/>
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B45" s="25">
@@ -10318,13 +10383,13 @@
         <v>8225.4465263262209</v>
       </c>
       <c r="AX45" s="1"/>
-      <c r="BC45" s="71"/>
-      <c r="BD45" s="71"/>
-      <c r="BE45" s="71"/>
-      <c r="BF45" s="71"/>
-      <c r="BG45" s="71"/>
-      <c r="BH45" s="71"/>
-      <c r="BI45" s="71"/>
+      <c r="BC45" s="69"/>
+      <c r="BD45" s="69"/>
+      <c r="BE45" s="69"/>
+      <c r="BF45" s="69"/>
+      <c r="BG45" s="69"/>
+      <c r="BH45" s="69"/>
+      <c r="BI45" s="69"/>
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B46" s="25">
@@ -10412,13 +10477,13 @@
       <c r="AV46" s="1"/>
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
-      <c r="BC46" s="71"/>
-      <c r="BD46" s="71"/>
-      <c r="BE46" s="71"/>
-      <c r="BF46" s="71"/>
-      <c r="BG46" s="71"/>
-      <c r="BH46" s="71"/>
-      <c r="BI46" s="71"/>
+      <c r="BC46" s="69"/>
+      <c r="BD46" s="69"/>
+      <c r="BE46" s="69"/>
+      <c r="BF46" s="69"/>
+      <c r="BG46" s="69"/>
+      <c r="BH46" s="69"/>
+      <c r="BI46" s="69"/>
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B47" s="25">
@@ -10509,13 +10574,13 @@
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
-      <c r="BC47" s="71"/>
-      <c r="BD47" s="71"/>
-      <c r="BE47" s="71"/>
-      <c r="BF47" s="71"/>
-      <c r="BG47" s="71"/>
-      <c r="BH47" s="71"/>
-      <c r="BI47" s="71"/>
+      <c r="BC47" s="69"/>
+      <c r="BD47" s="69"/>
+      <c r="BE47" s="69"/>
+      <c r="BF47" s="69"/>
+      <c r="BG47" s="69"/>
+      <c r="BH47" s="69"/>
+      <c r="BI47" s="69"/>
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B48" s="25">
@@ -10606,471 +10671,471 @@
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
       <c r="AX48" s="1"/>
-      <c r="BC48" s="71"/>
-      <c r="BD48" s="71"/>
-      <c r="BE48" s="71"/>
-      <c r="BF48" s="71"/>
-      <c r="BG48" s="71"/>
-      <c r="BH48" s="71"/>
-      <c r="BI48" s="71"/>
+      <c r="BC48" s="69"/>
+      <c r="BD48" s="69"/>
+      <c r="BE48" s="69"/>
+      <c r="BF48" s="69"/>
+      <c r="BG48" s="69"/>
+      <c r="BH48" s="69"/>
+      <c r="BI48" s="69"/>
     </row>
     <row r="49" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="B49" s="71"/>
-      <c r="C49" s="71"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="71"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="71"/>
-      <c r="H49" s="71"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="71"/>
-      <c r="K49" s="71"/>
-      <c r="L49" s="71"/>
-      <c r="M49" s="71"/>
-      <c r="N49" s="71"/>
-      <c r="O49" s="71"/>
-      <c r="P49" s="71"/>
-      <c r="Q49" s="71"/>
-      <c r="R49" s="71"/>
-      <c r="S49" s="71"/>
-      <c r="T49" s="71"/>
-      <c r="U49" s="71"/>
-      <c r="V49" s="71"/>
-      <c r="W49" s="71"/>
-      <c r="X49" s="71"/>
-      <c r="Y49" s="71"/>
-      <c r="Z49" s="71"/>
-      <c r="AA49" s="71"/>
-      <c r="AB49" s="71"/>
-      <c r="AC49" s="71"/>
-      <c r="AD49" s="71"/>
-      <c r="AE49" s="71"/>
-      <c r="AF49" s="71"/>
-      <c r="AG49" s="71"/>
-      <c r="AH49" s="71"/>
-      <c r="AI49" s="71"/>
-      <c r="AJ49" s="71"/>
-      <c r="AK49" s="71"/>
-      <c r="AL49" s="71"/>
-      <c r="AM49" s="71"/>
-      <c r="AN49" s="71"/>
-      <c r="AO49" s="71"/>
-      <c r="AP49" s="71"/>
-      <c r="AQ49" s="71"/>
-      <c r="AR49" s="71"/>
-      <c r="AS49" s="71"/>
-      <c r="AT49" s="71"/>
-      <c r="AU49" s="71"/>
-      <c r="AV49" s="71"/>
-      <c r="AW49" s="71"/>
-      <c r="BC49" s="71"/>
-      <c r="BD49" s="71"/>
-      <c r="BE49" s="71"/>
-      <c r="BF49" s="71"/>
-      <c r="BG49" s="71"/>
-      <c r="BH49" s="71"/>
-      <c r="BI49" s="71"/>
+      <c r="B49" s="69"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="69"/>
+      <c r="O49" s="69"/>
+      <c r="P49" s="69"/>
+      <c r="Q49" s="69"/>
+      <c r="R49" s="69"/>
+      <c r="S49" s="69"/>
+      <c r="T49" s="69"/>
+      <c r="U49" s="69"/>
+      <c r="V49" s="69"/>
+      <c r="W49" s="69"/>
+      <c r="X49" s="69"/>
+      <c r="Y49" s="69"/>
+      <c r="Z49" s="69"/>
+      <c r="AA49" s="69"/>
+      <c r="AB49" s="69"/>
+      <c r="AC49" s="69"/>
+      <c r="AD49" s="69"/>
+      <c r="AE49" s="69"/>
+      <c r="AF49" s="69"/>
+      <c r="AG49" s="69"/>
+      <c r="AH49" s="69"/>
+      <c r="AI49" s="69"/>
+      <c r="AJ49" s="69"/>
+      <c r="AK49" s="69"/>
+      <c r="AL49" s="69"/>
+      <c r="AM49" s="69"/>
+      <c r="AN49" s="69"/>
+      <c r="AO49" s="69"/>
+      <c r="AP49" s="69"/>
+      <c r="AQ49" s="69"/>
+      <c r="AR49" s="69"/>
+      <c r="AS49" s="69"/>
+      <c r="AT49" s="69"/>
+      <c r="AU49" s="69"/>
+      <c r="AV49" s="69"/>
+      <c r="AW49" s="69"/>
+      <c r="BC49" s="69"/>
+      <c r="BD49" s="69"/>
+      <c r="BE49" s="69"/>
+      <c r="BF49" s="69"/>
+      <c r="BG49" s="69"/>
+      <c r="BH49" s="69"/>
+      <c r="BI49" s="69"/>
     </row>
     <row r="50" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="B50" s="113" t="s">
+      <c r="B50" s="111" t="s">
         <v>23</v>
       </c>
       <c r="C50" t="str">
         <f>Scenario</f>
         <v>Bull</v>
       </c>
-      <c r="D50" s="113" t="s">
+      <c r="D50" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="114">
+      <c r="E50" s="112">
         <f>B41</f>
         <v>11072.990711807943</v>
       </c>
-      <c r="F50" s="71"/>
-      <c r="G50" s="71"/>
-      <c r="H50" s="71"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="113" t="s">
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="K50" s="114">
+      <c r="K50" s="112">
         <f>H41</f>
         <v>7226.8031010754294</v>
       </c>
-      <c r="L50" s="71"/>
-      <c r="M50" s="71"/>
-      <c r="N50" s="71"/>
-      <c r="O50" s="71"/>
-      <c r="P50" s="113" t="s">
+      <c r="L50" s="69"/>
+      <c r="M50" s="69"/>
+      <c r="N50" s="69"/>
+      <c r="O50" s="69"/>
+      <c r="P50" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="Q50" s="114">
+      <c r="Q50" s="112">
         <f>N41</f>
         <v>8826.3819318363585</v>
       </c>
-      <c r="R50" s="71"/>
-      <c r="S50" s="71"/>
-      <c r="T50" s="71"/>
-      <c r="U50" s="71"/>
-      <c r="V50" s="71"/>
-      <c r="W50" s="71"/>
-      <c r="X50" s="71"/>
-      <c r="Y50" s="71"/>
-      <c r="Z50" s="71"/>
-      <c r="AA50" s="71"/>
-      <c r="AB50" s="71"/>
-      <c r="AC50" s="71"/>
-      <c r="AD50" s="71"/>
-      <c r="AE50" s="71"/>
-      <c r="AF50" s="71"/>
-      <c r="AG50" s="71"/>
-      <c r="AH50" s="71"/>
-      <c r="AI50" s="71"/>
-      <c r="AJ50" s="71"/>
-      <c r="AK50" s="71"/>
-      <c r="AL50" s="71"/>
-      <c r="AM50" s="71"/>
-      <c r="AN50" s="71"/>
-      <c r="AO50" s="71"/>
-      <c r="AP50" s="71"/>
-      <c r="AQ50" s="71"/>
-      <c r="AR50" s="71"/>
-      <c r="AS50" s="71"/>
-      <c r="AT50" s="71"/>
-      <c r="AU50" s="71"/>
-      <c r="AV50" s="71"/>
-      <c r="AW50" s="71"/>
-      <c r="BC50" s="71"/>
-      <c r="BD50" s="71"/>
-      <c r="BE50" s="71"/>
-      <c r="BF50" s="71"/>
-      <c r="BG50" s="71"/>
-      <c r="BH50" s="71"/>
-      <c r="BI50" s="71"/>
+      <c r="R50" s="69"/>
+      <c r="S50" s="69"/>
+      <c r="T50" s="69"/>
+      <c r="U50" s="69"/>
+      <c r="V50" s="69"/>
+      <c r="W50" s="69"/>
+      <c r="X50" s="69"/>
+      <c r="Y50" s="69"/>
+      <c r="Z50" s="69"/>
+      <c r="AA50" s="69"/>
+      <c r="AB50" s="69"/>
+      <c r="AC50" s="69"/>
+      <c r="AD50" s="69"/>
+      <c r="AE50" s="69"/>
+      <c r="AF50" s="69"/>
+      <c r="AG50" s="69"/>
+      <c r="AH50" s="69"/>
+      <c r="AI50" s="69"/>
+      <c r="AJ50" s="69"/>
+      <c r="AK50" s="69"/>
+      <c r="AL50" s="69"/>
+      <c r="AM50" s="69"/>
+      <c r="AN50" s="69"/>
+      <c r="AO50" s="69"/>
+      <c r="AP50" s="69"/>
+      <c r="AQ50" s="69"/>
+      <c r="AR50" s="69"/>
+      <c r="AS50" s="69"/>
+      <c r="AT50" s="69"/>
+      <c r="AU50" s="69"/>
+      <c r="AV50" s="69"/>
+      <c r="AW50" s="69"/>
+      <c r="BC50" s="69"/>
+      <c r="BD50" s="69"/>
+      <c r="BE50" s="69"/>
+      <c r="BF50" s="69"/>
+      <c r="BG50" s="69"/>
+      <c r="BH50" s="69"/>
+      <c r="BI50" s="69"/>
     </row>
     <row r="51" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="B51" s="71"/>
-      <c r="C51" s="71"/>
-      <c r="D51" s="71"/>
-      <c r="E51" s="71"/>
-      <c r="F51" s="71"/>
-      <c r="G51" s="71"/>
-      <c r="H51" s="71"/>
-      <c r="I51" s="71"/>
-      <c r="J51" s="71"/>
-      <c r="K51" s="71"/>
-      <c r="L51" s="71"/>
-      <c r="M51" s="71"/>
-      <c r="N51" s="71"/>
-      <c r="O51" s="71"/>
-      <c r="P51" s="71"/>
-      <c r="Q51" s="71"/>
-      <c r="R51" s="71"/>
-      <c r="S51" s="71"/>
-      <c r="T51" s="71"/>
-      <c r="U51" s="71"/>
-      <c r="V51" s="71"/>
-      <c r="W51" s="71"/>
-      <c r="X51" s="71"/>
-      <c r="Y51" s="71"/>
-      <c r="Z51" s="71"/>
-      <c r="AA51" s="71"/>
-      <c r="AB51" s="71"/>
-      <c r="AC51" s="71"/>
-      <c r="AD51" s="71"/>
-      <c r="AE51" s="71"/>
-      <c r="AF51" s="71"/>
-      <c r="AG51" s="71"/>
-      <c r="AH51" s="71"/>
-      <c r="AI51" s="71"/>
-      <c r="AJ51" s="71"/>
-      <c r="AK51" s="71"/>
-      <c r="AL51" s="71"/>
-      <c r="AM51" s="71"/>
-      <c r="AN51" s="71"/>
-      <c r="AO51" s="71"/>
-      <c r="AP51" s="71"/>
-      <c r="AQ51" s="71"/>
-      <c r="AR51" s="71"/>
-      <c r="AS51" s="71"/>
-      <c r="AT51" s="71"/>
-      <c r="AU51" s="71"/>
-      <c r="AV51" s="71"/>
-      <c r="AW51" s="71"/>
-      <c r="BC51" s="71"/>
-      <c r="BD51" s="71"/>
-      <c r="BE51" s="71"/>
-      <c r="BF51" s="71"/>
-      <c r="BG51" s="71"/>
-      <c r="BH51" s="71"/>
-      <c r="BI51" s="71"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="69"/>
+      <c r="I51" s="69"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="69"/>
+      <c r="L51" s="69"/>
+      <c r="M51" s="69"/>
+      <c r="N51" s="69"/>
+      <c r="O51" s="69"/>
+      <c r="P51" s="69"/>
+      <c r="Q51" s="69"/>
+      <c r="R51" s="69"/>
+      <c r="S51" s="69"/>
+      <c r="T51" s="69"/>
+      <c r="U51" s="69"/>
+      <c r="V51" s="69"/>
+      <c r="W51" s="69"/>
+      <c r="X51" s="69"/>
+      <c r="Y51" s="69"/>
+      <c r="Z51" s="69"/>
+      <c r="AA51" s="69"/>
+      <c r="AB51" s="69"/>
+      <c r="AC51" s="69"/>
+      <c r="AD51" s="69"/>
+      <c r="AE51" s="69"/>
+      <c r="AF51" s="69"/>
+      <c r="AG51" s="69"/>
+      <c r="AH51" s="69"/>
+      <c r="AI51" s="69"/>
+      <c r="AJ51" s="69"/>
+      <c r="AK51" s="69"/>
+      <c r="AL51" s="69"/>
+      <c r="AM51" s="69"/>
+      <c r="AN51" s="69"/>
+      <c r="AO51" s="69"/>
+      <c r="AP51" s="69"/>
+      <c r="AQ51" s="69"/>
+      <c r="AR51" s="69"/>
+      <c r="AS51" s="69"/>
+      <c r="AT51" s="69"/>
+      <c r="AU51" s="69"/>
+      <c r="AV51" s="69"/>
+      <c r="AW51" s="69"/>
+      <c r="BC51" s="69"/>
+      <c r="BD51" s="69"/>
+      <c r="BE51" s="69"/>
+      <c r="BF51" s="69"/>
+      <c r="BG51" s="69"/>
+      <c r="BH51" s="69"/>
+      <c r="BI51" s="69"/>
     </row>
     <row r="52" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A52" s="115" t="s">
+      <c r="A52" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="113">
+      <c r="B52" s="111">
         <f>SOTP!B31</f>
         <v>2986</v>
       </c>
-      <c r="C52" s="71"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="71"/>
-      <c r="F52" s="71"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="71"/>
-      <c r="I52" s="71"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="71"/>
-      <c r="L52" s="71"/>
-      <c r="M52" s="71"/>
-      <c r="N52" s="71"/>
-      <c r="O52" s="71"/>
-      <c r="P52" s="71"/>
-      <c r="Q52" s="71"/>
-      <c r="R52" s="71"/>
-      <c r="S52" s="71"/>
-      <c r="T52" s="71"/>
-      <c r="U52" s="71"/>
-      <c r="V52" s="71"/>
-      <c r="W52" s="71"/>
-      <c r="X52" s="71"/>
-      <c r="Y52" s="71"/>
-      <c r="Z52" s="71"/>
-      <c r="AA52" s="71"/>
-      <c r="AB52" s="71"/>
-      <c r="AC52" s="71"/>
-      <c r="AD52" s="71"/>
-      <c r="AE52" s="71"/>
-      <c r="AF52" s="71"/>
-      <c r="AG52" s="71"/>
-      <c r="AH52" s="71"/>
-      <c r="AI52" s="71"/>
-      <c r="AJ52" s="71"/>
-      <c r="AK52" s="71"/>
-      <c r="AL52" s="71"/>
-      <c r="AM52" s="71"/>
-      <c r="AN52" s="71"/>
-      <c r="AO52" s="71"/>
-      <c r="AP52" s="71"/>
-      <c r="AQ52" s="71"/>
-      <c r="AR52" s="71"/>
-      <c r="AS52" s="71"/>
-      <c r="AT52" s="71"/>
-      <c r="AU52" s="71"/>
-      <c r="AV52" s="71"/>
-      <c r="AW52" s="71"/>
-      <c r="BC52" s="71"/>
-      <c r="BD52" s="71"/>
-      <c r="BE52" s="71"/>
-      <c r="BF52" s="71"/>
-      <c r="BG52" s="71"/>
-      <c r="BH52" s="71"/>
-      <c r="BI52" s="71"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="69"/>
+      <c r="L52" s="69"/>
+      <c r="M52" s="69"/>
+      <c r="N52" s="69"/>
+      <c r="O52" s="69"/>
+      <c r="P52" s="69"/>
+      <c r="Q52" s="69"/>
+      <c r="R52" s="69"/>
+      <c r="S52" s="69"/>
+      <c r="T52" s="69"/>
+      <c r="U52" s="69"/>
+      <c r="V52" s="69"/>
+      <c r="W52" s="69"/>
+      <c r="X52" s="69"/>
+      <c r="Y52" s="69"/>
+      <c r="Z52" s="69"/>
+      <c r="AA52" s="69"/>
+      <c r="AB52" s="69"/>
+      <c r="AC52" s="69"/>
+      <c r="AD52" s="69"/>
+      <c r="AE52" s="69"/>
+      <c r="AF52" s="69"/>
+      <c r="AG52" s="69"/>
+      <c r="AH52" s="69"/>
+      <c r="AI52" s="69"/>
+      <c r="AJ52" s="69"/>
+      <c r="AK52" s="69"/>
+      <c r="AL52" s="69"/>
+      <c r="AM52" s="69"/>
+      <c r="AN52" s="69"/>
+      <c r="AO52" s="69"/>
+      <c r="AP52" s="69"/>
+      <c r="AQ52" s="69"/>
+      <c r="AR52" s="69"/>
+      <c r="AS52" s="69"/>
+      <c r="AT52" s="69"/>
+      <c r="AU52" s="69"/>
+      <c r="AV52" s="69"/>
+      <c r="AW52" s="69"/>
+      <c r="BC52" s="69"/>
+      <c r="BD52" s="69"/>
+      <c r="BE52" s="69"/>
+      <c r="BF52" s="69"/>
+      <c r="BG52" s="69"/>
+      <c r="BH52" s="69"/>
+      <c r="BI52" s="69"/>
     </row>
     <row r="53" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A53" s="115" t="s">
+      <c r="A53" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="B53" s="113">
+      <c r="B53" s="111">
         <f>E50+K50+Q50-B52</f>
         <v>24140.175744719731</v>
       </c>
-      <c r="C53" s="71"/>
-      <c r="D53" s="71"/>
-      <c r="E53" s="71"/>
-      <c r="F53" s="71"/>
-      <c r="G53" s="71"/>
-      <c r="H53" s="71"/>
-      <c r="I53" s="71"/>
-      <c r="J53" s="71"/>
-      <c r="K53" s="71"/>
-      <c r="L53" s="71"/>
-      <c r="M53" s="71"/>
-      <c r="N53" s="71"/>
-      <c r="O53" s="71"/>
-      <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
-      <c r="R53" s="71"/>
-      <c r="S53" s="71"/>
-      <c r="T53" s="71"/>
-      <c r="U53" s="71"/>
-      <c r="V53" s="71"/>
-      <c r="W53" s="71"/>
-      <c r="X53" s="71"/>
-      <c r="Y53" s="71"/>
-      <c r="Z53" s="71"/>
-      <c r="AA53" s="71"/>
-      <c r="AB53" s="71"/>
-      <c r="AC53" s="71"/>
-      <c r="AD53" s="71"/>
-      <c r="AE53" s="71"/>
-      <c r="AF53" s="71"/>
-      <c r="AG53" s="71"/>
-      <c r="AH53" s="71"/>
-      <c r="AI53" s="71"/>
-      <c r="AJ53" s="71"/>
-      <c r="AK53" s="71"/>
-      <c r="AL53" s="71"/>
-      <c r="AM53" s="71"/>
-      <c r="AN53" s="71"/>
-      <c r="AO53" s="71"/>
-      <c r="AP53" s="71"/>
-      <c r="AQ53" s="71"/>
-      <c r="AR53" s="71"/>
-      <c r="AS53" s="71"/>
-      <c r="AT53" s="71"/>
-      <c r="AU53" s="71"/>
-      <c r="AV53" s="71"/>
-      <c r="AW53" s="71"/>
-      <c r="BC53" s="71"/>
-      <c r="BD53" s="71"/>
-      <c r="BE53" s="71"/>
-      <c r="BF53" s="71"/>
-      <c r="BG53" s="71"/>
-      <c r="BH53" s="71"/>
-      <c r="BI53" s="71"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="69"/>
+      <c r="L53" s="69"/>
+      <c r="M53" s="69"/>
+      <c r="N53" s="69"/>
+      <c r="O53" s="69"/>
+      <c r="P53" s="69"/>
+      <c r="Q53" s="69"/>
+      <c r="R53" s="69"/>
+      <c r="S53" s="69"/>
+      <c r="T53" s="69"/>
+      <c r="U53" s="69"/>
+      <c r="V53" s="69"/>
+      <c r="W53" s="69"/>
+      <c r="X53" s="69"/>
+      <c r="Y53" s="69"/>
+      <c r="Z53" s="69"/>
+      <c r="AA53" s="69"/>
+      <c r="AB53" s="69"/>
+      <c r="AC53" s="69"/>
+      <c r="AD53" s="69"/>
+      <c r="AE53" s="69"/>
+      <c r="AF53" s="69"/>
+      <c r="AG53" s="69"/>
+      <c r="AH53" s="69"/>
+      <c r="AI53" s="69"/>
+      <c r="AJ53" s="69"/>
+      <c r="AK53" s="69"/>
+      <c r="AL53" s="69"/>
+      <c r="AM53" s="69"/>
+      <c r="AN53" s="69"/>
+      <c r="AO53" s="69"/>
+      <c r="AP53" s="69"/>
+      <c r="AQ53" s="69"/>
+      <c r="AR53" s="69"/>
+      <c r="AS53" s="69"/>
+      <c r="AT53" s="69"/>
+      <c r="AU53" s="69"/>
+      <c r="AV53" s="69"/>
+      <c r="AW53" s="69"/>
+      <c r="BC53" s="69"/>
+      <c r="BD53" s="69"/>
+      <c r="BE53" s="69"/>
+      <c r="BF53" s="69"/>
+      <c r="BG53" s="69"/>
+      <c r="BH53" s="69"/>
+      <c r="BI53" s="69"/>
     </row>
     <row r="54" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A54" s="115" t="s">
+      <c r="A54" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="127">
+      <c r="B54" s="125">
         <f>B53/DCF!B36</f>
         <v>27.557278247396951</v>
       </c>
-      <c r="C54" s="71"/>
-      <c r="D54" s="71"/>
-      <c r="E54" s="71"/>
-      <c r="F54" s="71"/>
-      <c r="G54" s="71"/>
-      <c r="H54" s="71"/>
-      <c r="I54" s="71"/>
-      <c r="J54" s="71"/>
-      <c r="K54" s="71"/>
-      <c r="L54" s="71"/>
-      <c r="M54" s="71"/>
-      <c r="N54" s="71"/>
-      <c r="O54" s="71"/>
-      <c r="P54" s="71"/>
-      <c r="Q54" s="71"/>
-      <c r="R54" s="71"/>
-      <c r="S54" s="71"/>
-      <c r="T54" s="71"/>
-      <c r="U54" s="71"/>
-      <c r="V54" s="71"/>
-      <c r="W54" s="71"/>
-      <c r="X54" s="71"/>
-      <c r="Y54" s="71"/>
-      <c r="Z54" s="71"/>
-      <c r="AA54" s="71"/>
-      <c r="AB54" s="71"/>
-      <c r="AC54" s="71"/>
-      <c r="AD54" s="71"/>
-      <c r="AE54" s="71"/>
-      <c r="AF54" s="71"/>
-      <c r="AG54" s="71"/>
-      <c r="AH54" s="71"/>
-      <c r="AI54" s="71"/>
-      <c r="AJ54" s="71"/>
-      <c r="AK54" s="71"/>
-      <c r="AL54" s="71"/>
-      <c r="AM54" s="71"/>
-      <c r="AN54" s="71"/>
-      <c r="AO54" s="71"/>
-      <c r="AP54" s="71"/>
-      <c r="AQ54" s="71"/>
-      <c r="AR54" s="71"/>
-      <c r="AS54" s="71"/>
-      <c r="AT54" s="71"/>
-      <c r="AU54" s="71"/>
-      <c r="AV54" s="71"/>
-      <c r="AW54" s="71"/>
-      <c r="BC54" s="71"/>
-      <c r="BD54" s="71"/>
-      <c r="BE54" s="71"/>
-      <c r="BF54" s="71"/>
-      <c r="BG54" s="71"/>
-      <c r="BH54" s="71"/>
-      <c r="BI54" s="71"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="69"/>
+      <c r="J54" s="69"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="69"/>
+      <c r="M54" s="69"/>
+      <c r="N54" s="69"/>
+      <c r="O54" s="69"/>
+      <c r="P54" s="69"/>
+      <c r="Q54" s="69"/>
+      <c r="R54" s="69"/>
+      <c r="S54" s="69"/>
+      <c r="T54" s="69"/>
+      <c r="U54" s="69"/>
+      <c r="V54" s="69"/>
+      <c r="W54" s="69"/>
+      <c r="X54" s="69"/>
+      <c r="Y54" s="69"/>
+      <c r="Z54" s="69"/>
+      <c r="AA54" s="69"/>
+      <c r="AB54" s="69"/>
+      <c r="AC54" s="69"/>
+      <c r="AD54" s="69"/>
+      <c r="AE54" s="69"/>
+      <c r="AF54" s="69"/>
+      <c r="AG54" s="69"/>
+      <c r="AH54" s="69"/>
+      <c r="AI54" s="69"/>
+      <c r="AJ54" s="69"/>
+      <c r="AK54" s="69"/>
+      <c r="AL54" s="69"/>
+      <c r="AM54" s="69"/>
+      <c r="AN54" s="69"/>
+      <c r="AO54" s="69"/>
+      <c r="AP54" s="69"/>
+      <c r="AQ54" s="69"/>
+      <c r="AR54" s="69"/>
+      <c r="AS54" s="69"/>
+      <c r="AT54" s="69"/>
+      <c r="AU54" s="69"/>
+      <c r="AV54" s="69"/>
+      <c r="AW54" s="69"/>
+      <c r="BC54" s="69"/>
+      <c r="BD54" s="69"/>
+      <c r="BE54" s="69"/>
+      <c r="BF54" s="69"/>
+      <c r="BG54" s="69"/>
+      <c r="BH54" s="69"/>
+      <c r="BI54" s="69"/>
     </row>
     <row r="55" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A55" s="115" t="s">
+      <c r="A55" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="127">
+      <c r="B55" s="125">
         <f>B54*2</f>
         <v>55.114556494793902</v>
       </c>
-      <c r="C55" s="71"/>
-      <c r="D55" s="71"/>
-      <c r="E55" s="71"/>
-      <c r="F55" s="71"/>
-      <c r="G55" s="71"/>
-      <c r="H55" s="71"/>
-      <c r="I55" s="71"/>
-      <c r="J55" s="71"/>
-      <c r="K55" s="71"/>
-      <c r="L55" s="71"/>
-      <c r="M55" s="71"/>
-      <c r="N55" s="71"/>
-      <c r="O55" s="71"/>
-      <c r="P55" s="71"/>
-      <c r="Q55" s="71"/>
-      <c r="R55" s="71"/>
-      <c r="S55" s="71"/>
-      <c r="T55" s="71"/>
-      <c r="U55" s="71"/>
-      <c r="V55" s="71"/>
-      <c r="W55" s="71"/>
-      <c r="X55" s="71"/>
-      <c r="Y55" s="71"/>
-      <c r="Z55" s="71"/>
-      <c r="AA55" s="71"/>
-      <c r="AB55" s="71"/>
-      <c r="AC55" s="71"/>
-      <c r="AD55" s="71"/>
-      <c r="AE55" s="71"/>
-      <c r="AF55" s="71"/>
-      <c r="AG55" s="71"/>
-      <c r="AH55" s="71"/>
-      <c r="AI55" s="71"/>
-      <c r="AJ55" s="71"/>
-      <c r="AK55" s="71"/>
-      <c r="AL55" s="71"/>
-      <c r="AM55" s="71"/>
-      <c r="AN55" s="71"/>
-      <c r="AO55" s="71"/>
-      <c r="AP55" s="71"/>
-      <c r="AQ55" s="71"/>
-      <c r="AR55" s="71"/>
-      <c r="AS55" s="71"/>
-      <c r="AT55" s="71"/>
-      <c r="AU55" s="71"/>
-      <c r="AV55" s="71"/>
-      <c r="AW55" s="71"/>
-      <c r="BC55" s="71"/>
-      <c r="BD55" s="71"/>
-      <c r="BE55" s="71"/>
-      <c r="BF55" s="71"/>
-      <c r="BG55" s="71"/>
-      <c r="BH55" s="71"/>
-      <c r="BI55" s="71"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+      <c r="K55" s="69"/>
+      <c r="L55" s="69"/>
+      <c r="M55" s="69"/>
+      <c r="N55" s="69"/>
+      <c r="O55" s="69"/>
+      <c r="P55" s="69"/>
+      <c r="Q55" s="69"/>
+      <c r="R55" s="69"/>
+      <c r="S55" s="69"/>
+      <c r="T55" s="69"/>
+      <c r="U55" s="69"/>
+      <c r="V55" s="69"/>
+      <c r="W55" s="69"/>
+      <c r="X55" s="69"/>
+      <c r="Y55" s="69"/>
+      <c r="Z55" s="69"/>
+      <c r="AA55" s="69"/>
+      <c r="AB55" s="69"/>
+      <c r="AC55" s="69"/>
+      <c r="AD55" s="69"/>
+      <c r="AE55" s="69"/>
+      <c r="AF55" s="69"/>
+      <c r="AG55" s="69"/>
+      <c r="AH55" s="69"/>
+      <c r="AI55" s="69"/>
+      <c r="AJ55" s="69"/>
+      <c r="AK55" s="69"/>
+      <c r="AL55" s="69"/>
+      <c r="AM55" s="69"/>
+      <c r="AN55" s="69"/>
+      <c r="AO55" s="69"/>
+      <c r="AP55" s="69"/>
+      <c r="AQ55" s="69"/>
+      <c r="AR55" s="69"/>
+      <c r="AS55" s="69"/>
+      <c r="AT55" s="69"/>
+      <c r="AU55" s="69"/>
+      <c r="AV55" s="69"/>
+      <c r="AW55" s="69"/>
+      <c r="BC55" s="69"/>
+      <c r="BD55" s="69"/>
+      <c r="BE55" s="69"/>
+      <c r="BF55" s="69"/>
+      <c r="BG55" s="69"/>
+      <c r="BH55" s="69"/>
+      <c r="BI55" s="69"/>
     </row>
     <row r="56" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A56" s="115" t="s">
+      <c r="A56" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="127">
+      <c r="B56" s="125">
         <f>SOTP!B35</f>
         <v>36.82</v>
       </c>
     </row>
     <row r="57" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A57" s="115" t="s">
+      <c r="A57" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="127">
+      <c r="B57" s="125">
         <f>B55-B56</f>
         <v>18.294556494793902</v>
       </c>
